--- a/georgia_ev_intelligence/outputs/parent_chunks.xlsx
+++ b/georgia_ev_intelligence/outputs/parent_chunks.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KB_ROW_0000_5e57606e87f2</t>
+          <t>KB_ROW_0000_b2df76566378</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -444,9 +444,9 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0000_5e57606e87f2
+          <t>Record ID: KB_ROW_0000_b2df76566378
 Source Row ID: 0
-Company: ACM Georgia LLC
+Company: acm georgia llc
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: Warrenton, Warren County
@@ -468,7 +468,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KB_ROW_0001_2f4c0eb610f7</t>
+          <t>KB_ROW_0001_8049b9fe3e39</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,9 +476,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0001_2f4c0eb610f7
+          <t>Record ID: KB_ROW_0001_8049b9fe3e39
 Source Row ID: 1
-Company: Adient
+Company: adient
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: West Point, Harris County
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KB_ROW_0002_020dd409fd98</t>
+          <t>KB_ROW_0002_9f0f6aa64876</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -508,9 +508,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0002_020dd409fd98
+          <t>Record ID: KB_ROW_0002_9f0f6aa64876
 Source Row ID: 2
-Company: ADVICS Manufacturing Georgia LLC
+Company: advics manufacturing georgia llc
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: LaGrange, Troup County
@@ -532,7 +532,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KB_ROW_0003_cf847be96faa</t>
+          <t>KB_ROW_0003_d3e2ede2d2b7</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -540,9 +540,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0003_cf847be96faa
+          <t>Record ID: KB_ROW_0003_d3e2ede2d2b7
 Source Row ID: 3
-Company: Ajin Georgia
+Company: ajin georgia
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: Register, Bulloch County
@@ -564,7 +564,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KB_ROW_0004_d4bff4ee5eac</t>
+          <t>KB_ROW_0004_25227b7e5143</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -572,9 +572,9 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0004_d4bff4ee5eac
+          <t>Record ID: KB_ROW_0004_25227b7e5143
 Source Row ID: 4
-Company: ALBAform Inc.
+Company: albaform inc.
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: Flowery Branch, Hall County
@@ -596,7 +596,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KB_ROW_0005_114d69d15021</t>
+          <t>KB_ROW_0005_365c809018a7</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -604,9 +604,9 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0005_114d69d15021
+          <t>Record ID: KB_ROW_0005_365c809018a7
 Source Row ID: 5
-Company: Anovion Technologies
+Company: anovion technologies
 Category: Tier 2/3
 Industry Group: Textile Products
 Updated Location: Bainbridge
@@ -628,7 +628,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KB_ROW_0006_8321aa0dc02a</t>
+          <t>KB_ROW_0006_38c92108bf1e</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -636,9 +636,9 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0006_8321aa0dc02a
+          <t>Record ID: KB_ROW_0006_38c92108bf1e
 Source Row ID: 6
-Company: Apache Mills Inc.
+Company: apache mills inc.
 Category: Tier 2/3
 Industry Group: Paper and Allied Products
 Updated Location: Calhoun, Hall County
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KB_ROW_0007_7d995f400768</t>
+          <t>KB_ROW_0007_8c7960365e2c</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -668,9 +668,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0007_7d995f400768
+          <t>Record ID: KB_ROW_0007_8c7960365e2c
 Source Row ID: 7
-Company: Archer Aviation Inc.
+Company: archer aviation inc.
 Category: Tier 2/3
 Industry Group: Chemicals and Allied Products
 Updated Location: Covington, Morgan County
@@ -692,7 +692,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KB_ROW_0008_d6d6a73c2640</t>
+          <t>KB_ROW_0008_5a574f27c743</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -700,9 +700,9 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0008_d6d6a73c2640
+          <t>Record ID: KB_ROW_0008_5a574f27c743
 Source Row ID: 8
-Company: Arising Industries Inc.
+Company: arising industries inc.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Norcross, Gwinnett County
@@ -724,7 +724,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KB_ROW_0009_67fa56c46d4a</t>
+          <t>KB_ROW_0009_09ae68758810</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -732,9 +732,9 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0009_67fa56c46d4a
+          <t>Record ID: KB_ROW_0009_09ae68758810
 Source Row ID: 9
-Company: Arising Industries Inc.
+Company: arising industries inc.
 Category: Tier 2/3
 Industry Group: Chemicals and Allied Products
 Updated Location: Norcross, Gwinnett County
@@ -756,7 +756,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KB_ROW_0010_dcb13ba56e59</t>
+          <t>KB_ROW_0010_17c5f98fb5ff</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -764,9 +764,9 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0010_dcb13ba56e59
+          <t>Record ID: KB_ROW_0010_17c5f98fb5ff
 Source Row ID: 10
-Company: Ascend Elements
+Company: ascend elements
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Henry County
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KB_ROW_0011_adcdcf7f91b5</t>
+          <t>KB_ROW_0011_7db3b61dfdc4</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -796,9 +796,9 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0011_adcdcf7f91b5
+          <t>Record ID: KB_ROW_0011_7db3b61dfdc4
 Source Row ID: 11
-Company: Aspen Aerogels
+Company: aspen aerogels
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Statesboro
@@ -820,7 +820,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KB_ROW_0012_a9eeee666e32</t>
+          <t>KB_ROW_0012_3cb6f3046164</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -828,9 +828,9 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0012_a9eeee666e32
+          <t>Record ID: KB_ROW_0012_3cb6f3046164
 Source Row ID: 12
-Company: Aurubis
+Company: aurubis
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Augusta, Richmond County
@@ -852,7 +852,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KB_ROW_0013_24412d8a914d</t>
+          <t>KB_ROW_0013_cef4694165ed</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -860,9 +860,9 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0013_24412d8a914d
+          <t>Record ID: KB_ROW_0013_cef4694165ed
 Source Row ID: 13
-Company: AVS
+Company: avs
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Alpharetta, Forsyth County
@@ -884,7 +884,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KB_ROW_0014_e2acd9c2e05b</t>
+          <t>KB_ROW_0014_e7ce1a24a9a6</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -892,9 +892,9 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0014_e2acd9c2e05b
+          <t>Record ID: KB_ROW_0014_e7ce1a24a9a6
 Source Row ID: 14
-Company: Beaver Manufacturing Co. Inc.
+Company: beaver manufacturing co. inc.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Mansfield, Newton County
@@ -916,7 +916,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KB_ROW_0015_08ed9bb8308e</t>
+          <t>KB_ROW_0015_8a968bf95d37</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -924,9 +924,9 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0015_08ed9bb8308e
+          <t>Record ID: KB_ROW_0015_8a968bf95d37
 Source Row ID: 15
-Company: Big Tex Trailer Manufacturing Inc.
+Company: big tex trailer manufacturing inc.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Loganville, Gwinnett County
@@ -948,7 +948,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KB_ROW_0016_caf4575e5d2d</t>
+          <t>KB_ROW_0016_5bad83ba9ff7</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -956,9 +956,9 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0016_caf4575e5d2d
+          <t>Record ID: KB_ROW_0016_5bad83ba9ff7
 Source Row ID: 16
-Company: Blue Bird Corp.
+Company: blue bird corp.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Fort Valley, Peach County
@@ -980,7 +980,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KB_ROW_0017_84b229b76045</t>
+          <t>KB_ROW_0017_41b44e8bb02b</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -988,9 +988,9 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0017_84b229b76045
+          <t>Record ID: KB_ROW_0017_41b44e8bb02b
 Source Row ID: 17
-Company: Blue Ridge Manufacturing
+Company: blue ridge manufacturing
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Blue Ridge, Union County
@@ -1012,7 +1012,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KB_ROW_0018_1f10fe496f8f</t>
+          <t>KB_ROW_0018_c4bab3bd8d3f</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1020,9 +1020,9 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0018_1f10fe496f8f
+          <t>Record ID: KB_ROW_0018_c4bab3bd8d3f
 Source Row ID: 18
-Company: Bonnell Aluminum
+Company: bonnell aluminum
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Newnan, Coweta County
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KB_ROW_0019_073b29f53c73</t>
+          <t>KB_ROW_0019_0c35b3a5f9da</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1052,9 +1052,9 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0019_073b29f53c73
+          <t>Record ID: KB_ROW_0019_0c35b3a5f9da
 Source Row ID: 19
-Company: Boogook Industries
+Company: boogook industries
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Macon, Bibb County
@@ -1076,7 +1076,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KB_ROW_0020_8b4a5bbfaf55</t>
+          <t>KB_ROW_0020_9dd25f6fa489</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1084,9 +1084,9 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0020_8b4a5bbfaf55
+          <t>Record ID: KB_ROW_0020_9dd25f6fa489
 Source Row ID: 20
-Company: Bosal Industries Georgia
+Company: bosal industries georgia
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Lavonia, Franklin County
@@ -1108,7 +1108,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KB_ROW_0021_f5863fd4d37a</t>
+          <t>KB_ROW_0021_7caa76813ba6</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1116,9 +1116,9 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0021_f5863fd4d37a
+          <t>Record ID: KB_ROW_0021_7caa76813ba6
 Source Row ID: 21
-Company: Bosch (Automotive Division)
+Company: bosch (automotive division)
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Toccoa, Stephens County
@@ -1140,7 +1140,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KB_ROW_0022_5eeb470ecb5c</t>
+          <t>KB_ROW_0022_f5ff4992c373</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1148,9 +1148,9 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0022_5eeb470ecb5c
+          <t>Record ID: KB_ROW_0022_f5ff4992c373
 Source Row ID: 22
-Company: Bridgestone Bandag
+Company: bridgestone bandag
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Griffin, Spalding County
@@ -1172,7 +1172,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KB_ROW_0023_d129e3771d67</t>
+          <t>KB_ROW_0023_2bc94f11d5fb</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1180,9 +1180,9 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0023_d129e3771d67
+          <t>Record ID: KB_ROW_0023_2bc94f11d5fb
 Source Row ID: 23
-Company: Carcoustics USA
+Company: carcoustics usa
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Buford, Gwinnett County
@@ -1204,7 +1204,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KB_ROW_0024_48c4bf95c95b</t>
+          <t>KB_ROW_0024_e0096a532bb6</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1212,9 +1212,9 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0024_48c4bf95c95b
+          <t>Record ID: KB_ROW_0024_e0096a532bb6
 Source Row ID: 24
-Company: Club Car LLC
+Company: club car llc
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Evans, Columbia County
@@ -1236,7 +1236,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KB_ROW_0025_0829dcd9b773</t>
+          <t>KB_ROW_0025_3ac8473ef485</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1244,9 +1244,9 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0025_0829dcd9b773
+          <t>Record ID: KB_ROW_0025_3ac8473ef485
 Source Row ID: 25
-Company: Constellium Automotive USA
+Company: constellium automotive usa
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Cartersville, Bartow County
@@ -1268,7 +1268,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KB_ROW_0026_d1c3da7e9ef4</t>
+          <t>KB_ROW_0026_ff8c43430dad</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1276,9 +1276,9 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0026_d1c3da7e9ef4
+          <t>Record ID: KB_ROW_0026_ff8c43430dad
 Source Row ID: 26
-Company: Continental Automotive
+Company: continental automotive
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Fairburn, Fulton County
@@ -1300,7 +1300,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KB_ROW_0027_8247461b2da4</t>
+          <t>KB_ROW_0027_30ab6d69c97a</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1308,9 +1308,9 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0027_8247461b2da4
+          <t>Record ID: KB_ROW_0027_30ab6d69c97a
 Source Row ID: 27
-Company: Continental Tire the Americas LLC
+Company: continental tire the americas llc
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Barnesville, Lamar County
@@ -1332,7 +1332,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KB_ROW_0028_90a3da25396d</t>
+          <t>KB_ROW_0028_a903eb543e2f</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1340,9 +1340,9 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0028_90a3da25396d
+          <t>Record ID: KB_ROW_0028_a903eb543e2f
 Source Row ID: 28
-Company: DaeChang Seat Company
+Company: daechang seat company
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Savannah, Chatham County
@@ -1364,7 +1364,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KB_ROW_0029_89fe602e3129</t>
+          <t>KB_ROW_0029_50616c531f09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1372,9 +1372,9 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0029_89fe602e3129
+          <t>Record ID: KB_ROW_0029_50616c531f09
 Source Row ID: 29
-Company: DAEHAN Solution Georgia LLC
+Company: daehan solution georgia llc
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Henry County
@@ -1396,7 +1396,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KB_ROW_0030_ffacf3085d89</t>
+          <t>KB_ROW_0030_0a1023c0bf47</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1404,9 +1404,9 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0030_ffacf3085d89
+          <t>Record ID: KB_ROW_0030_0a1023c0bf47
 Source Row ID: 30
-Company: Daesol Ausys
+Company: daesol ausys
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Smyrna, Cobb County
@@ -1428,7 +1428,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KB_ROW_0031_44411488fb25</t>
+          <t>KB_ROW_0031_1a8bc04d1912</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1436,9 +1436,9 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0031_44411488fb25
+          <t>Record ID: KB_ROW_0031_1a8bc04d1912
 Source Row ID: 31
-Company: Daesol Material Georgia, LLC
+Company: daesol material georgia, llc
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Duluth, Gwinnett County
@@ -1460,7 +1460,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KB_ROW_0032_21f06e666bd6</t>
+          <t>KB_ROW_0032_1eb959820857</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1468,9 +1468,9 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0032_21f06e666bd6
+          <t>Record ID: KB_ROW_0032_1eb959820857
 Source Row ID: 32
-Company: Daimler Truck North America
+Company: daimler truck north america
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Newton County
@@ -1492,7 +1492,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KB_ROW_0033_af9a853d940a</t>
+          <t>KB_ROW_0033_44f759076fb8</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1500,9 +1500,9 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0033_af9a853d940a
+          <t>Record ID: KB_ROW_0033_44f759076fb8
 Source Row ID: 33
-Company: DAS Corp.
+Company: das corp.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Metter, Candler County
@@ -1524,7 +1524,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KB_ROW_0034_8961aca2cb80</t>
+          <t>KB_ROW_0034_84363828fdee</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1532,9 +1532,9 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0034_8961aca2cb80
+          <t>Record ID: KB_ROW_0034_84363828fdee
 Source Row ID: 34
-Company: Decostar Industries
+Company: decostar industries
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Buchanan, Polk County
@@ -1556,7 +1556,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KB_ROW_0035_c9c2f60b1a70</t>
+          <t>KB_ROW_0035_b29382ee7991</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1564,9 +1564,9 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0035_c9c2f60b1a70
+          <t>Record ID: KB_ROW_0035_b29382ee7991
 Source Row ID: 35
-Company: DeKalb Tool &amp; Die Inc.
+Company: dekalb tool &amp; die inc.
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Tucker, DeKalb County
@@ -1588,7 +1588,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KB_ROW_0036_e7a9bd1f04b5</t>
+          <t>KB_ROW_0036_8a4190ee16e4</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1596,9 +1596,9 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0036_e7a9bd1f04b5
+          <t>Record ID: KB_ROW_0036_8a4190ee16e4
 Source Row ID: 36
-Company: Denkai America
+Company: denkai america
 Category: Tier 2/3
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Augusta, Richmond County
@@ -1620,7 +1620,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KB_ROW_0037_1ed49e58af1e</t>
+          <t>KB_ROW_0037_1e1c4bb22100</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1628,9 +1628,9 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0037_1ed49e58af1e
+          <t>Record ID: KB_ROW_0037_1e1c4bb22100
 Source Row ID: 37
-Company: Denso Manufacturing Georgia
+Company: denso manufacturing georgia
 Category: Tier 2/3
 Industry Group: Stone, Clay, Glass and Concrete Products
 Updated Location: Pendergrass, Jackson County
@@ -1652,7 +1652,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KB_ROW_0038_7c5f40eb6c7b</t>
+          <t>KB_ROW_0038_7c9dd250f85e</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1660,9 +1660,9 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0038_7c5f40eb6c7b
+          <t>Record ID: KB_ROW_0038_7c9dd250f85e
 Source Row ID: 38
-Company: Die-Tech Industries Inc.
+Company: die-tech industries inc.
 Category: Tier 2/3
 Industry Group: Stone, Clay, Glass and Concrete Products
 Updated Location: Carrollton, Carroll County
@@ -1684,7 +1684,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KB_ROW_0039_f342a95e0e11</t>
+          <t>KB_ROW_0039_80b909f2af2c</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1692,9 +1692,9 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0039_f342a95e0e11
+          <t>Record ID: KB_ROW_0039_80b909f2af2c
 Source Row ID: 39
-Company: Dinex Emissions Inc.
+Company: dinex emissions inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Dublin, Laurens County
@@ -1716,7 +1716,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KB_ROW_0040_3f804b8e260d</t>
+          <t>KB_ROW_0040_f918aca6e8d1</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1724,9 +1724,9 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0040_3f804b8e260d
+          <t>Record ID: KB_ROW_0040_f918aca6e8d1
 Source Row ID: 40
-Company: Dongwon Autopart Technology Georgia LLC
+Company: dongwon autopart technology georgia llc
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Hogansville, Meriwether County
@@ -1748,7 +1748,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KB_ROW_0041_631fe42c2064</t>
+          <t>KB_ROW_0041_a0bf37f81ea3</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1756,9 +1756,9 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0041_631fe42c2064
+          <t>Record ID: KB_ROW_0041_a0bf37f81ea3
 Source Row ID: 41
-Company: Dorsett Industries Inc.
+Company: dorsett industries inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Dalton, Whitfield County
@@ -1780,7 +1780,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KB_ROW_0042_c8c3430587d7</t>
+          <t>KB_ROW_0042_59716335fc80</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1788,9 +1788,9 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0042_c8c3430587d7
+          <t>Record ID: KB_ROW_0042_59716335fc80
 Source Row ID: 42
-Company: Down 2 Earth Trailers
+Company: down 2 earth trailers
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Baxley, Appling County
@@ -1812,7 +1812,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KB_ROW_0043_16c4f7a91461</t>
+          <t>KB_ROW_0043_34bffdb8d0b5</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1820,9 +1820,9 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0043_16c4f7a91461
+          <t>Record ID: KB_ROW_0043_34bffdb8d0b5
 Source Row ID: 43
-Company: Duckyang
+Company: duckyang
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Braselton, Jackson County
@@ -1844,7 +1844,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KB_ROW_0044_5927163b90a2</t>
+          <t>KB_ROW_0044_3eb46a97bcda</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1852,9 +1852,9 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0044_5927163b90a2
+          <t>Record ID: KB_ROW_0044_3eb46a97bcda
 Source Row ID: 44
-Company: Eaton Corp.
+Company: eaton corp.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Athens, Clarke County
@@ -1876,7 +1876,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KB_ROW_0045_4a7c003d3ddb</t>
+          <t>KB_ROW_0045_5f84137fddea</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1884,9 +1884,9 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0045_4a7c003d3ddb
+          <t>Record ID: KB_ROW_0045_5f84137fddea
 Source Row ID: 45
-Company: Ecoplastic America Corporation
+Company: ecoplastic america corporation
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Register, Bulloch County
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KB_ROW_0046_9b9ae213b322</t>
+          <t>KB_ROW_0046_2e97852909c1</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1916,9 +1916,9 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0046_9b9ae213b322
+          <t>Record ID: KB_ROW_0046_2e97852909c1
 Source Row ID: 46
-Company: Ecoplastic Corporation
+Company: ecoplastic corporation
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Statesboro, Bulloch County
@@ -1940,7 +1940,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KB_ROW_0047_847f499ae6b7</t>
+          <t>KB_ROW_0047_6bd005cafe15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1948,9 +1948,9 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0047_847f499ae6b7
+          <t>Record ID: KB_ROW_0047_6bd005cafe15
 Source Row ID: 47
-Company: Elan Technology Inc.
+Company: elan technology inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Midway, Liberty County
@@ -1972,7 +1972,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KB_ROW_0048_78e785b19d8b</t>
+          <t>KB_ROW_0048_3a115293fa7e</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1980,9 +1980,9 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0048_78e785b19d8b
+          <t>Record ID: KB_ROW_0048_3a115293fa7e
 Source Row ID: 48
-Company: Enchem America Inc.
+Company: enchem america inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Commerce, Jackson County
@@ -2004,7 +2004,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KB_ROW_0049_19804504fe90</t>
+          <t>KB_ROW_0049_3c463b37cb25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2012,9 +2012,9 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0049_19804504fe90
+          <t>Record ID: KB_ROW_0049_3c463b37cb25
 Source Row ID: 49
-Company: Enplas USA Inc.
+Company: enplas usa inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Marietta, Cobb County
@@ -2036,7 +2036,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KB_ROW_0050_72da17be7889</t>
+          <t>KB_ROW_0050_fa1b5dc4d601</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2044,9 +2044,9 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0050_72da17be7889
+          <t>Record ID: KB_ROW_0050_fa1b5dc4d601
 Source Row ID: 50
-Company: Erdrich USA Inc.
+Company: erdrich usa inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Dublin, Laurens County
@@ -2068,7 +2068,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KB_ROW_0051_6d949abf5fb3</t>
+          <t>KB_ROW_0051_59729ac6a1ff</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2076,9 +2076,9 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0051_6d949abf5fb3
+          <t>Record ID: KB_ROW_0051_59729ac6a1ff
 Source Row ID: 51
-Company: EVCO Plastics
+Company: evco plastics
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Calhoun, Gordon County
@@ -2100,7 +2100,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KB_ROW_0052_5f4c2fca5532</t>
+          <t>KB_ROW_0052_140973bc03b6</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2108,9 +2108,9 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0052_5f4c2fca5532
+          <t>Record ID: KB_ROW_0052_140973bc03b6
 Source Row ID: 52
-Company: F&amp;P Georgia Manufacturing
+Company: f&amp;p georgia manufacturing
 Category: Tier 1/2
 Industry Group: Primary Metal Industries
 Updated Location: Rome, Floyd County
@@ -2132,7 +2132,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KB_ROW_0053_a9c1fd3380df</t>
+          <t>KB_ROW_0053_ce4efb740a6e</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2140,9 +2140,9 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0053_a9c1fd3380df
+          <t>Record ID: KB_ROW_0053_ce4efb740a6e
 Source Row ID: 53
-Company: Fanello Industries Inc.
+Company: fanello industries inc.
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Lavonia, Franklin County
@@ -2164,7 +2164,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KB_ROW_0054_fde81202652a</t>
+          <t>KB_ROW_0054_71bd500ed129</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2172,9 +2172,9 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0054_fde81202652a
+          <t>Record ID: KB_ROW_0054_71bd500ed129
 Source Row ID: 54
-Company: First American Resources
+Company: first american resources
 Category: Tier 2/3
 Industry Group: Primary Metal Industries
 Updated Location: Mableton, Cobb County
@@ -2196,7 +2196,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KB_ROW_0055_be52551e8c76</t>
+          <t>KB_ROW_0055_f4e46116742e</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2204,9 +2204,9 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0055_be52551e8c76
+          <t>Record ID: KB_ROW_0055_f4e46116742e
 Source Row ID: 55
-Company: Flambeau Inc.
+Company: flambeau inc.
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Madison, Morgan County
@@ -2228,7 +2228,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KB_ROW_0056_3f58162e4958</t>
+          <t>KB_ROW_0056_b64c96ea346e</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2236,9 +2236,9 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0056_3f58162e4958
+          <t>Record ID: KB_ROW_0056_b64c96ea346e
 Source Row ID: 56
-Company: Fouts Brothers Fire Equipment
+Company: fouts brothers fire equipment
 Category: Tier 1/2
 Industry Group: Fabricated Metal Products
 Updated Location: Milledgeville, Baldwin County
@@ -2260,7 +2260,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KB_ROW_0057_079fd52623b9</t>
+          <t>KB_ROW_0057_0d9827b4555d</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2268,9 +2268,9 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0057_079fd52623b9
+          <t>Record ID: KB_ROW_0057_0d9827b4555d
 Source Row ID: 57
-Company: FOX Factory
+Company: fox factory
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Duluth, Gwinnett County
@@ -2292,7 +2292,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KB_ROW_0058_8fea8f45eda3</t>
+          <t>KB_ROW_0058_c2618420fd76</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2300,9 +2300,9 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0058_8fea8f45eda3
+          <t>Record ID: KB_ROW_0058_c2618420fd76
 Source Row ID: 58
-Company: Freudenberg-NOK
+Company: freudenberg-nok
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: LaGrange, Troup County
@@ -2324,7 +2324,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KB_ROW_0059_cd464afe1ee7</t>
+          <t>KB_ROW_0059_15de10f5c43e</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2332,9 +2332,9 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0059_cd464afe1ee7
+          <t>Record ID: KB_ROW_0059_15de10f5c43e
 Source Row ID: 59
-Company: Freudenberg-NOK
+Company: freudenberg-nok
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: LaGrange, Troup County
@@ -2356,7 +2356,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KB_ROW_0060_21928f38cd2a</t>
+          <t>KB_ROW_0060_bf5e951a6ff4</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2364,9 +2364,9 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0060_21928f38cd2a
+          <t>Record ID: KB_ROW_0060_bf5e951a6ff4
 Source Row ID: 60
-Company: FREYR Battery
+Company: freyr battery
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Atlanta, Fulton County
@@ -2388,7 +2388,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KB_ROW_0061_462a539bcd5b</t>
+          <t>KB_ROW_0061_715613f2c976</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2396,9 +2396,9 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0061_462a539bcd5b
+          <t>Record ID: KB_ROW_0061_715613f2c976
 Source Row ID: 61
-Company: GEDIA Georgia LLC
+Company: gedia georgia llc
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Dalton, Fulton County
@@ -2420,7 +2420,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KB_ROW_0062_01872aa4bf22</t>
+          <t>KB_ROW_0062_7440247a086e</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2428,9 +2428,9 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0062_01872aa4bf22
+          <t>Record ID: KB_ROW_0062_7440247a086e
 Source Row ID: 62
-Company: Global Powertrain Systems LLC
+Company: global powertrain systems llc
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Jefferson, Jackson County
@@ -2452,7 +2452,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KB_ROW_0063_6169b93b1229</t>
+          <t>KB_ROW_0063_34052dbd7ec4</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2460,9 +2460,9 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0063_6169b93b1229
+          <t>Record ID: KB_ROW_0063_34052dbd7ec4
 Source Row ID: 63
-Company: GLOVIS Georgia LLC
+Company: glovis georgia llc
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
@@ -2484,7 +2484,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KB_ROW_0064_8bb2cf30a90e</t>
+          <t>KB_ROW_0064_a194fe9799e4</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2492,9 +2492,9 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0064_8bb2cf30a90e
+          <t>Record ID: KB_ROW_0064_a194fe9799e4
 Source Row ID: 64
-Company: Goodyear Tire &amp; Rubber Co.
+Company: goodyear tire &amp; rubber co.
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Atlanta, Clayton County
@@ -2516,7 +2516,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KB_ROW_0065_5815e89e0f84</t>
+          <t>KB_ROW_0065_f8a5fd3ba42f</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2524,9 +2524,9 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0065_5815e89e0f84
+          <t>Record ID: KB_ROW_0065_f8a5fd3ba42f
 Source Row ID: 65
-Company: Great Dane LP
+Company: great dane lp
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
@@ -2548,7 +2548,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KB_ROW_0066_41208047ecf6</t>
+          <t>KB_ROW_0066_155f98b55007</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2556,9 +2556,9 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0066_41208047ecf6
+          <t>Record ID: KB_ROW_0066_155f98b55007
 Source Row ID: 66
-Company: Great Dane Trailers
+Company: great dane trailers
 Category: Tier 2/3
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
@@ -2580,7 +2580,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KB_ROW_0067_485997c3ac2b</t>
+          <t>KB_ROW_0067_467270662cf3</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2588,9 +2588,9 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0067_485997c3ac2b
+          <t>Record ID: KB_ROW_0067_467270662cf3
 Source Row ID: 67
-Company: Grudem
+Company: grudem
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Gainesville, Hall County
@@ -2612,7 +2612,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KB_ROW_0068_4fc9fcfa0ac0</t>
+          <t>KB_ROW_0068_c80b147209b2</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2620,9 +2620,9 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0068_4fc9fcfa0ac0
+          <t>Record ID: KB_ROW_0068_c80b147209b2
 Source Row ID: 68
-Company: GSC Steel Stamping LLC
+Company: gsc steel stamping llc
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Adairsville, Bartow County
@@ -2644,7 +2644,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KB_ROW_0069_1f17755e78d3</t>
+          <t>KB_ROW_0069_cc6f1a5a64b4</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2652,9 +2652,9 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0069_1f17755e78d3
+          <t>Record ID: KB_ROW_0069_cc6f1a5a64b4
 Source Row ID: 69
-Company: Haering Precision USA LP
+Company: haering precision usa lp
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Buford, Hall County
@@ -2676,7 +2676,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KB_ROW_0070_fa746f8c93e6</t>
+          <t>KB_ROW_0070_56fe7fef09cc</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2684,9 +2684,9 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0070_fa746f8c93e6
+          <t>Record ID: KB_ROW_0070_56fe7fef09cc
 Source Row ID: 70
-Company: Haering Precision USA LP
+Company: haering precision usa lp
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Buford, Hall County
@@ -2708,7 +2708,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KB_ROW_0071_eb091d45480e</t>
+          <t>KB_ROW_0071_5cd8a46e00ad</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2716,9 +2716,9 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0071_eb091d45480e
+          <t>Record ID: KB_ROW_0071_5cd8a46e00ad
 Source Row ID: 71
-Company: Hanon Systems USA LLC
+Company: hanon systems usa llc
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Shorter, Harris County
@@ -2740,7 +2740,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KB_ROW_0072_a20318e5c28f</t>
+          <t>KB_ROW_0072_ae42badb5bf3</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2748,9 +2748,9 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0072_a20318e5c28f
+          <t>Record ID: KB_ROW_0072_ae42badb5bf3
 Source Row ID: 72
-Company: HELLA Automotive Sales Inc.
+Company: hella automotive sales inc.
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Atlanta, Cobb County
@@ -2772,7 +2772,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KB_ROW_0073_cb9045fdff56</t>
+          <t>KB_ROW_0073_f49871d5b969</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2780,9 +2780,9 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0073_cb9045fdff56
+          <t>Record ID: KB_ROW_0073_f49871d5b969
 Source Row ID: 73
-Company: HEXPOL Compounding Corp.
+Company: hexpol compounding corp.
 Category: Tier 2/3
 Industry Group: Machinery Except Electrical
 Updated Location: Griffin, Spalding County
@@ -2794,7 +2794,7 @@
 Primary OEMs: Multiple OEMs
 Supplier or Affiliation Type: Automotive supply chain participant
 Employment: 50.0
-Product / Service: Automotive and commercial stampings; metalworking dies
+Product / Service: Automotive and commercial stampings ; metalworking dies
 EV / Battery Relevant: Indirect
 Classification Method: Supplier
 Original Row ID: 73</t>
@@ -2804,7 +2804,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KB_ROW_0074_b97142d14b7e</t>
+          <t>KB_ROW_0074_2495f9f5b7b7</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2812,9 +2812,9 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0074_b97142d14b7e
+          <t>Record ID: KB_ROW_0074_2495f9f5b7b7
 Source Row ID: 74
-Company: Hitachi Astemo
+Company: hitachi astemo
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Shorter, Harris County
@@ -2836,7 +2836,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KB_ROW_0075_818c28509246</t>
+          <t>KB_ROW_0075_eaa6e1be60da</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2844,9 +2844,9 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0075_818c28509246
+          <t>Record ID: KB_ROW_0075_eaa6e1be60da
 Source Row ID: 75
-Company: Hitachi Astemo Americas Inc.
+Company: hitachi astemo americas inc.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Shorter, Harris County
@@ -2868,7 +2868,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KB_ROW_0076_b647e1e6373e</t>
+          <t>KB_ROW_0076_f5f881d2d9ba</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2876,9 +2876,9 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0076_b647e1e6373e
+          <t>Record ID: KB_ROW_0076_f5f881d2d9ba
 Source Row ID: 76
-Company: Hollingsworth &amp; Vose Co.
+Company: hollingsworth &amp; vose co.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Hawkinsville, Pulaski County
@@ -2900,7 +2900,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KB_ROW_0077_938481c427a0</t>
+          <t>KB_ROW_0077_b853a834945a</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2908,9 +2908,9 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0077_938481c427a0
+          <t>Record ID: KB_ROW_0077_b853a834945a
 Source Row ID: 77
-Company: Honda Development &amp; Manufacturing
+Company: honda development &amp; manufacturing
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Tallapoosa, Cherokee County
@@ -2932,7 +2932,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KB_ROW_0078_09a293b8ace1</t>
+          <t>KB_ROW_0078_6d80d62e3c7b</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2940,9 +2940,9 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0078_09a293b8ace1
+          <t>Record ID: KB_ROW_0078_6d80d62e3c7b
 Source Row ID: 78
-Company: Hwashin
+Company: hwashin
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: LaGrange, Haralson County
@@ -2964,7 +2964,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KB_ROW_0079_fd33dcc5b185</t>
+          <t>KB_ROW_0079_1190b0e94739</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2972,9 +2972,9 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0079_fd33dcc5b185
+          <t>Record ID: KB_ROW_0079_1190b0e94739
 Source Row ID: 79
-Company: Hyundai &amp; LG Energy Solution (LGES)
+Company: hyundai &amp; lg energy solution (lges)
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Chatham County
@@ -2996,7 +2996,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KB_ROW_0080_4b40bef28172</t>
+          <t>KB_ROW_0080_fc28aab64288</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3004,9 +3004,9 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0080_4b40bef28172
+          <t>Record ID: KB_ROW_0080_fc28aab64288
 Source Row ID: 80
-Company: Hyundai Industrial Co.
+Company: hyundai industrial co.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Chatham County
@@ -3028,7 +3028,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KB_ROW_0081_3caf71df70c4</t>
+          <t>KB_ROW_0081_ad9464e1812e</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3036,9 +3036,9 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0081_3caf71df70c4
+          <t>Record ID: KB_ROW_0081_ad9464e1812e
 Source Row ID: 81
-Company: Hyundai MOBIS (Georgia)
+Company: hyundai mobis (georgia)
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
@@ -3060,7 +3060,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KB_ROW_0082_4ad6202e0a85</t>
+          <t>KB_ROW_0082_03c590458ceb</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3068,9 +3068,9 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0082_4ad6202e0a85
+          <t>Record ID: KB_ROW_0082_03c590458ceb
 Source Row ID: 82
-Company: Hyundai Motor Group
+Company: hyundai motor group
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Bryan County
@@ -3092,7 +3092,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KB_ROW_0083_e0d1f3d6ee08</t>
+          <t>KB_ROW_0083_2d267f6d5adb</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3100,9 +3100,9 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0083_e0d1f3d6ee08
+          <t>Record ID: KB_ROW_0083_2d267f6d5adb
 Source Row ID: 83
-Company: Hyundai Transys Georgia Powertrain
+Company: hyundai transys georgia powertrain
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
@@ -3124,7 +3124,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KB_ROW_0084_7927eab6b472</t>
+          <t>KB_ROW_0084_93b34277a833</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3132,9 +3132,9 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0084_7927eab6b472
+          <t>Record ID: KB_ROW_0084_93b34277a833
 Source Row ID: 84
-Company: Hyundai Transys Georgia Seating Systems
+Company: hyundai transys georgia seating systems
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
@@ -3156,7 +3156,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KB_ROW_0085_c06cf3cdbf26</t>
+          <t>KB_ROW_0085_c46b9255bfde</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3164,9 +3164,9 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0085_c06cf3cdbf26
+          <t>Record ID: KB_ROW_0085_c46b9255bfde
 Source Row ID: 85
-Company: IMMI
+Company: immi
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Dublin, Laurens County
@@ -3188,7 +3188,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KB_ROW_0086_b1f0c2bb7bc1</t>
+          <t>KB_ROW_0086_e2388e6d634f</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3196,9 +3196,9 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0086_b1f0c2bb7bc1
+          <t>Record ID: KB_ROW_0086_e2388e6d634f
 Source Row ID: 86
-Company: IMS Gear Georgia Inc.
+Company: ims gear georgia inc.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Suwanee, Gwinnett County
@@ -3220,7 +3220,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KB_ROW_0087_6e88cd9a4b35</t>
+          <t>KB_ROW_0087_df8721a5fb43</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3228,9 +3228,9 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0087_6e88cd9a4b35
+          <t>Record ID: KB_ROW_0087_df8721a5fb43
 Source Row ID: 87
-Company: Inalfa Roof Systems Inc.
+Company: inalfa roof systems inc.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Acworth, Cobb County
@@ -3252,7 +3252,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KB_ROW_0088_5dc739de54cf</t>
+          <t>KB_ROW_0088_8b950028531f</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3260,9 +3260,9 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0088_5dc739de54cf
+          <t>Record ID: KB_ROW_0088_8b950028531f
 Source Row ID: 88
-Company: JAC Products Inc.
+Company: jac products inc.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Jefferson, Jackson County
@@ -3284,7 +3284,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KB_ROW_0089_b631462d9a20</t>
+          <t>KB_ROW_0089_0252725a3ded</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3292,9 +3292,9 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0089_b631462d9a20
+          <t>Record ID: KB_ROW_0089_0252725a3ded
 Source Row ID: 89
-Company: Jefferson Southern Corp.
+Company: jefferson southern corp.
 Category: Tier 1/2
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Commerce, Forsyth County
@@ -3316,7 +3316,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KB_ROW_0090_4cd7992237bc</t>
+          <t>KB_ROW_0090_b77384c14664</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3324,9 +3324,9 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0090_4cd7992237bc
+          <t>Record ID: KB_ROW_0090_b77384c14664
 Source Row ID: 90
-Company: Jefferson Southern Corporation
+Company: jefferson southern corporation
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Commerce, Forsyth County
@@ -3348,7 +3348,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KB_ROW_0091_f2a866c26c85</t>
+          <t>KB_ROW_0091_4d766dd9f747</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3356,9 +3356,9 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0091_f2a866c26c85
+          <t>Record ID: KB_ROW_0091_4d766dd9f747
 Source Row ID: 91
-Company: Joon Georgia, Inc.
+Company: joon georgia, inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: West Point, Chattahoochee County
@@ -3380,7 +3380,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KB_ROW_0092_0b73e6ea1c9d</t>
+          <t>KB_ROW_0092_ecc223424833</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3388,9 +3388,9 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0092_0b73e6ea1c9d
+          <t>Record ID: KB_ROW_0092_ecc223424833
 Source Row ID: 92
-Company: JTEKT North America Corp.
+Company: jtekt north america corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Pendergrass, Jackson County
@@ -3412,7 +3412,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KB_ROW_0093_7d14f04c1a1c</t>
+          <t>KB_ROW_0093_7201c262aaa8</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3420,9 +3420,9 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0093_7d14f04c1a1c
+          <t>Record ID: KB_ROW_0093_7201c262aaa8
 Source Row ID: 93
-Company: Kautex Inc.
+Company: kautex inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Lavonia, Rabun County
@@ -3444,7 +3444,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KB_ROW_0094_ff945844f7a4</t>
+          <t>KB_ROW_0094_929e9abd1626</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3452,9 +3452,9 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0094_ff945844f7a4
+          <t>Record ID: KB_ROW_0094_929e9abd1626
 Source Row ID: 94
-Company: Kia Georgia Inc.
+Company: kia georgia inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
@@ -3476,7 +3476,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KB_ROW_0095_6120dc4654fb</t>
+          <t>KB_ROW_0095_e1941583a052</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3484,9 +3484,9 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0095_6120dc4654fb
+          <t>Record ID: KB_ROW_0095_e1941583a052
 Source Row ID: 95
-Company: KTX America Corporation
+Company: ktx america corporation
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Meriwether County
@@ -3508,7 +3508,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KB_ROW_0096_6214bfb853ee</t>
+          <t>KB_ROW_0096_c965290c6157</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3516,9 +3516,9 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0096_6214bfb853ee
+          <t>Record ID: KB_ROW_0096_c965290c6157
 Source Row ID: 96
-Company: Kumho Tire USA Inc.
+Company: kumho tire usa inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Macon, Bibb County
@@ -3540,7 +3540,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KB_ROW_0097_d1e1ed301ce4</t>
+          <t>KB_ROW_0097_74543880f6e5</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3548,9 +3548,9 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0097_d1e1ed301ce4
+          <t>Record ID: KB_ROW_0097_74543880f6e5
 Source Row ID: 97
-Company: Kyungshin America Corp.
+Company: kyungshin america corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
@@ -3572,7 +3572,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KB_ROW_0098_b2dd6471bd4c</t>
+          <t>KB_ROW_0098_6a3156d82ece</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3580,9 +3580,9 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0098_b2dd6471bd4c
+          <t>Record ID: KB_ROW_0098_6a3156d82ece
 Source Row ID: 98
-Company: Lark United Manufacturing Inc.
+Company: lark united manufacturing inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Laurens County
@@ -3604,7 +3604,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KB_ROW_0099_f8677a50be90</t>
+          <t>KB_ROW_0099_a6e6d7b24e3a</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3612,9 +3612,9 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0099_f8677a50be90
+          <t>Record ID: KB_ROW_0099_a6e6d7b24e3a
 Source Row ID: 99
-Company: Lear Corporation
+Company: lear corporation
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Hammond Industrial Park, Troup County
@@ -3636,7 +3636,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KB_ROW_0100_7847adef73ca</t>
+          <t>KB_ROW_0100_de96faddf2d2</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -3644,9 +3644,9 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0100_7847adef73ca
+          <t>Record ID: KB_ROW_0100_de96faddf2d2
 Source Row ID: 100
-Company: Lehigh Technologies Inc.
+Company: lehigh technologies inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Tucker, Walton County
@@ -3668,7 +3668,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KB_ROW_0101_a2bb2d1640fe</t>
+          <t>KB_ROW_0101_92aa1f39fa19</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3676,9 +3676,9 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0101_a2bb2d1640fe
+          <t>Record ID: KB_ROW_0101_92aa1f39fa19
 Source Row ID: 101
-Company: Linde + Wiemann
+Company: linde + wiemann
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Laurens County
@@ -3700,7 +3700,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KB_ROW_0102_ae54ccc7a8f0</t>
+          <t>KB_ROW_0102_844f3c23cefe</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3708,9 +3708,9 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0102_ae54ccc7a8f0
+          <t>Record ID: KB_ROW_0102_844f3c23cefe
 Source Row ID: 102
-Company: Lund International Inc.
+Company: lund international inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Madison, Morgan County
@@ -3732,7 +3732,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KB_ROW_0103_b90e17a4624f</t>
+          <t>KB_ROW_0103_eb3c8969be98</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3740,9 +3740,9 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0103_b90e17a4624f
+          <t>Record ID: KB_ROW_0103_eb3c8969be98
 Source Row ID: 103
-Company: Lund International Inc./Ventshade Division
+Company: lund international inc./ventshade division
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Madison, Morgan County
@@ -3764,7 +3764,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KB_ROW_0104_1d5d17167a81</t>
+          <t>KB_ROW_0104_851b9d7de437</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3772,9 +3772,9 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0104_1d5d17167a81
+          <t>Record ID: KB_ROW_0104_851b9d7de437
 Source Row ID: 104
-Company: Lyle Industries Inc.
+Company: lyle industries inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dawsonville, Dawson County
@@ -3796,7 +3796,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KB_ROW_0105_89351df33e0d</t>
+          <t>KB_ROW_0105_5ad782d81b5d</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3804,9 +3804,9 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0105_89351df33e0d
+          <t>Record ID: KB_ROW_0105_5ad782d81b5d
 Source Row ID: 105
-Company: Lyle Industries Inc.
+Company: lyle industries inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dawsonville, Dawson County
@@ -3828,7 +3828,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KB_ROW_0106_8178dae66ac4</t>
+          <t>KB_ROW_0106_c7fd3db6d1b2</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3836,9 +3836,9 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0106_8178dae66ac4
+          <t>Record ID: KB_ROW_0106_c7fd3db6d1b2
 Source Row ID: 106
-Company: Mack Trucks
+Company: mack trucks
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Lowndes County
@@ -3860,7 +3860,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KB_ROW_0107_638b3c7c1c0c</t>
+          <t>KB_ROW_0107_1f3e334c93c4</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3868,9 +3868,9 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0107_638b3c7c1c0c
+          <t>Record ID: KB_ROW_0107_1f3e334c93c4
 Source Row ID: 107
-Company: Magna International
+Company: magna international
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Carrollton, Carroll County
@@ -3892,7 +3892,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KB_ROW_0108_26484cc9c17c</t>
+          <t>KB_ROW_0108_b77e5233eff1</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3900,9 +3900,9 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0108_26484cc9c17c
+          <t>Record ID: KB_ROW_0108_b77e5233eff1
 Source Row ID: 108
-Company: Mando America Corp.
+Company: mando america corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Hogansville, Meriwether County
@@ -3924,7 +3924,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KB_ROW_0109_26c7982e029b</t>
+          <t>KB_ROW_0109_3a62ffe60895</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3932,9 +3932,9 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0109_26c7982e029b
+          <t>Record ID: KB_ROW_0109_3a62ffe60895
 Source Row ID: 109
-Company: Master Craft Engineering Inc.
+Company: master craft engineering inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Lavonia, Franklin County
@@ -3956,7 +3956,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KB_ROW_0110_4be560e28ad9</t>
+          <t>KB_ROW_0110_a72f58d3e8c1</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3964,9 +3964,9 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0110_4be560e28ad9
+          <t>Record ID: KB_ROW_0110_a72f58d3e8c1
 Source Row ID: 110
-Company: MAT Heavy Duty
+Company: mat heavy duty
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Gwinnett County
@@ -3988,7 +3988,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KB_ROW_0111_72e48ea1b818</t>
+          <t>KB_ROW_0111_143ae0426538</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3996,9 +3996,9 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0111_72e48ea1b818
+          <t>Record ID: KB_ROW_0111_143ae0426538
 Source Row ID: 111
-Company: Maxxis International USA
+Company: maxxis international usa
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Clayton County
@@ -4020,7 +4020,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KB_ROW_0112_bbf73d08455f</t>
+          <t>KB_ROW_0112_5dd7150cde91</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4028,9 +4028,9 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0112_bbf73d08455f
+          <t>Record ID: KB_ROW_0112_5dd7150cde91
 Source Row ID: 112
-Company: Mercedes-Benz USA LLC
+Company: mercedes-benz usa llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Sandy Springs, Fulton County
@@ -4052,7 +4052,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KB_ROW_0113_e464e5d4c8c5</t>
+          <t>KB_ROW_0113_30da37886659</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4060,9 +4060,9 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0113_e464e5d4c8c5
+          <t>Record ID: KB_ROW_0113_30da37886659
 Source Row ID: 113
-Company: Michelin Tread Technologies
+Company: michelin tread technologies
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Hart County
@@ -4084,7 +4084,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KB_ROW_0114_055f451e00fd</t>
+          <t>KB_ROW_0114_4c49b610f9ef</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4092,9 +4092,9 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0114_055f451e00fd
+          <t>Record ID: KB_ROW_0114_4c49b610f9ef
 Source Row ID: 114
-Company: Milliken &amp; Co./Valway Plant
+Company: milliken &amp; co./valway plant
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
@@ -4116,7 +4116,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KB_ROW_0115_4df3e7044c44</t>
+          <t>KB_ROW_0115_124f936ecef2</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -4124,9 +4124,9 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0115_4df3e7044c44
+          <t>Record ID: KB_ROW_0115_124f936ecef2
 Source Row ID: 115
-Company: Minebea AccessSolutions USA Inc.
+Company: minebea accesssolutions usa inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Gainesville, Fulton County
@@ -4148,7 +4148,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KB_ROW_0116_4a7dd41ad6e7</t>
+          <t>KB_ROW_0116_6bb42c415a08</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -4156,9 +4156,9 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0116_4a7dd41ad6e7
+          <t>Record ID: KB_ROW_0116_6bb42c415a08
 Source Row ID: 116
-Company: Mobis Alabama LLC
+Company: mobis alabama llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
@@ -4180,7 +4180,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KB_ROW_0117_6b599b0af694</t>
+          <t>KB_ROW_0117_e1a5c31cd9ce</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -4188,9 +4188,9 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0117_6b599b0af694
+          <t>Record ID: KB_ROW_0117_e1a5c31cd9ce
 Source Row ID: 117
-Company: MollerTech LLC
+Company: mollertech llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dalton, Whitfield County
@@ -4212,7 +4212,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KB_ROW_0118_aee0ce1a471d</t>
+          <t>KB_ROW_0118_3d9f4b981222</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -4220,9 +4220,9 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0118_aee0ce1a471d
+          <t>Record ID: KB_ROW_0118_3d9f4b981222
 Source Row ID: 118
-Company: Morgan Corp.
+Company: morgan corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Rabun County
@@ -4244,7 +4244,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KB_ROW_0119_9208fefc8288</t>
+          <t>KB_ROW_0119_884ba9afa5ca</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -4252,9 +4252,9 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0119_9208fefc8288
+          <t>Record ID: KB_ROW_0119_884ba9afa5ca
 Source Row ID: 119
-Company: Murata Electronics North America Inc.
+Company: murata electronics north america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Smyrna, Paulding County
@@ -4276,7 +4276,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KB_ROW_0120_5fb2a8f9b550</t>
+          <t>KB_ROW_0120_390cca53104a</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -4284,9 +4284,9 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0120_5fb2a8f9b550
+          <t>Record ID: KB_ROW_0120_390cca53104a
 Source Row ID: 120
-Company: Neaton Rome Inc.
+Company: neaton rome inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Rome, Douglas County
@@ -4308,7 +4308,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KB_ROW_0121_f9828c5b519a</t>
+          <t>KB_ROW_0121_8e76a4d1763d</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -4316,9 +4316,9 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0121_f9828c5b519a
+          <t>Record ID: KB_ROW_0121_8e76a4d1763d
 Source Row ID: 121
-Company: Nidec Elesys Americas Corp.
+Company: nidec elesys americas corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Forsyth County
@@ -4340,7 +4340,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KB_ROW_0122_f3788bb2b61c</t>
+          <t>KB_ROW_0122_599275d68c81</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4348,9 +4348,9 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0122_f3788bb2b61c
+          <t>Record ID: KB_ROW_0122_599275d68c81
 Source Row ID: 122
-Company: NIFCO KTW America Corp.
+Company: nifco ktw america corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Toccoa, Stephens County
@@ -4372,7 +4372,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KB_ROW_0123_93b8ae7a8e77</t>
+          <t>KB_ROW_0123_dd8df2ebaf54</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4380,9 +4380,9 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0123_93b8ae7a8e77
+          <t>Record ID: KB_ROW_0123_dd8df2ebaf54
 Source Row ID: 123
-Company: Nile Automotive
+Company: nile automotive
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Cumming, Forsyth County
@@ -4404,7 +4404,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KB_ROW_0124_2cc83de6dafb</t>
+          <t>KB_ROW_0124_aef2eb691e57</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -4412,9 +4412,9 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0124_2cc83de6dafb
+          <t>Record ID: KB_ROW_0124_aef2eb691e57
 Source Row ID: 124
-Company: Nisshinbo Automotive Manufacturing Inc.
+Company: nisshinbo automotive manufacturing inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Covington, Newton County
@@ -4436,7 +4436,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>KB_ROW_0125_1936612a7c06</t>
+          <t>KB_ROW_0125_dc491619a8e5</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4444,9 +4444,9 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0125_1936612a7c06
+          <t>Record ID: KB_ROW_0125_dc491619a8e5
 Source Row ID: 125
-Company: Nivel Parts &amp; Manufacturing Co. LLC
+Company: nivel parts &amp; manufacturing co. llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Cairo, Grady County
@@ -4468,7 +4468,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KB_ROW_0126_2429ef1852bf</t>
+          <t>KB_ROW_0126_2b6e04d2fab4</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -4476,9 +4476,9 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0126_2429ef1852bf
+          <t>Record ID: KB_ROW_0126_2b6e04d2fab4
 Source Row ID: 126
-Company: Novelis Inc.
+Company: novelis inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
@@ -4500,7 +4500,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KB_ROW_0127_cec1fb6ab594</t>
+          <t>KB_ROW_0127_1a8514009557</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -4508,9 +4508,9 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0127_cec1fb6ab594
+          <t>Record ID: KB_ROW_0127_1a8514009557
 Source Row ID: 127
-Company: Novelis Inc.
+Company: novelis inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
@@ -4532,7 +4532,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KB_ROW_0128_91f077053fcd</t>
+          <t>KB_ROW_0128_7439a38ddceb</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4540,9 +4540,9 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0128_91f077053fcd
+          <t>Record ID: KB_ROW_0128_7439a38ddceb
 Source Row ID: 128
-Company: Novelis Inc.
+Company: novelis inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
@@ -4564,7 +4564,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KB_ROW_0129_6dee43f45e63</t>
+          <t>KB_ROW_0129_e5f2afdf1ca2</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -4572,9 +4572,9 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0129_6dee43f45e63
+          <t>Record ID: KB_ROW_0129_e5f2afdf1ca2
 Source Row ID: 129
-Company: NVH Korea
+Company: nvh korea
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Locust Grove, Henry County
@@ -4596,7 +4596,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KB_ROW_0130_57b234b0a039</t>
+          <t>KB_ROW_0130_24f5af66f2db</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -4604,9 +4604,9 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0130_57b234b0a039
+          <t>Record ID: KB_ROW_0130_24f5af66f2db
 Source Row ID: 130
-Company: Oneda Corp.
+Company: oneda corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Gainesville, Hall County
@@ -4628,7 +4628,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KB_ROW_0131_23bf3b0c17eb</t>
+          <t>KB_ROW_0131_63f1fe9fe19a</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -4636,9 +4636,9 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0131_23bf3b0c17eb
+          <t>Record ID: KB_ROW_0131_63f1fe9fe19a
 Source Row ID: 131
-Company: OTR Wheel Engineering Inc.
+Company: otr wheel engineering inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Rome, Floyd County
@@ -4660,7 +4660,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KB_ROW_0132_7597c9b64e4f</t>
+          <t>KB_ROW_0132_d06e231b57af</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -4668,9 +4668,9 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0132_7597c9b64e4f
+          <t>Record ID: KB_ROW_0132_d06e231b57af
 Source Row ID: 132
-Company: Paccar
+Company: paccar
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Morrow, Clayton County
@@ -4692,7 +4692,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KB_ROW_0133_ad83e81b0c15</t>
+          <t>KB_ROW_0133_46b1f8e970af</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4700,9 +4700,9 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0133_ad83e81b0c15
+          <t>Record ID: KB_ROW_0133_46b1f8e970af
 Source Row ID: 133
-Company: PAI Industries Inc.
+Company: pai industries inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Mableton, Cobb County
@@ -4724,7 +4724,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>KB_ROW_0134_5a41ad5f9005</t>
+          <t>KB_ROW_0134_53d0a2b407db</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -4732,9 +4732,9 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0134_5a41ad5f9005
+          <t>Record ID: KB_ROW_0134_53d0a2b407db
 Source Row ID: 134
-Company: Pak-Lite Inc.
+Company: pak-lite inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Gwinnett County
@@ -4756,7 +4756,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KB_ROW_0135_e846a53bed37</t>
+          <t>KB_ROW_0135_56daed95445d</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -4764,9 +4764,9 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0135_e846a53bed37
+          <t>Record ID: KB_ROW_0135_56daed95445d
 Source Row ID: 135
-Company: Panasonic Automotive Systems Co.
+Company: panasonic automotive systems co.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Fayette County
@@ -4788,7 +4788,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KB_ROW_0136_85272980589b</t>
+          <t>KB_ROW_0136_20ebf372b583</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -4796,9 +4796,9 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0136_85272980589b
+          <t>Record ID: KB_ROW_0136_20ebf372b583
 Source Row ID: 136
-Company: Panasonic Automotive Systems Co.
+Company: panasonic automotive systems co.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Fayette County
@@ -4810,7 +4810,7 @@
 Primary OEMs: Multiple OEMs
 Supplier or Affiliation Type: Automotive supply chain participant
 Employment: 175.0
-Product / Service: Fluid carrying systems; steel pipe and tubes; powertrain and plastic tank systems
+Product / Service: Fluid carrying systems ; steel pipe and tubes ; powertrain and plastic tank systems
 EV / Battery Relevant: Indirect
 Classification Method: Supplier
 Original Row ID: 136</t>
@@ -4820,7 +4820,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KB_ROW_0137_88ccc9002fca</t>
+          <t>KB_ROW_0137_ffaab067034d</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -4828,9 +4828,9 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0137_88ccc9002fca
+          <t>Record ID: KB_ROW_0137_ffaab067034d
 Source Row ID: 137
-Company: Panduit Corp.
+Company: panduit corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Cumming, Forsyth County
@@ -4852,7 +4852,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KB_ROW_0138_ff2077bd1835</t>
+          <t>KB_ROW_0138_857e4fab235d</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -4860,9 +4860,9 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0138_ff2077bd1835
+          <t>Record ID: KB_ROW_0138_857e4fab235d
 Source Row ID: 138
-Company: Peerless-Winsmith Inc.
+Company: peerless-winsmith inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Flowery Branch, Hall County
@@ -4884,7 +4884,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KB_ROW_0139_a2cffdfc4ec2</t>
+          <t>KB_ROW_0139_c97f74b04ac9</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4892,9 +4892,9 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0139_a2cffdfc4ec2
+          <t>Record ID: KB_ROW_0139_c97f74b04ac9
 Source Row ID: 139
-Company: Perkins Small Engines LLC
+Company: perkins small engines llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Griffin, Spalding County
@@ -4916,7 +4916,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KB_ROW_0140_9cb314ef4085</t>
+          <t>KB_ROW_0140_748ab8f7f767</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -4924,9 +4924,9 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0140_9cb314ef4085
+          <t>Record ID: KB_ROW_0140_748ab8f7f767
 Source Row ID: 140
-Company: Peterson Spring
+Company: peterson spring
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Athens, Clarke County
@@ -4948,7 +4948,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KB_ROW_0141_b3749d050478</t>
+          <t>KB_ROW_0141_f29401df7fc9</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4956,9 +4956,9 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0141_b3749d050478
+          <t>Record ID: KB_ROW_0141_f29401df7fc9
 Source Row ID: 141
-Company: PHA Body Systems LLC
+Company: pha body systems llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Bloomingdale, Chatham County
@@ -4980,7 +4980,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KB_ROW_0142_8afa6083b795</t>
+          <t>KB_ROW_0142_0e8c8fcb6958</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4988,9 +4988,9 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0142_8afa6083b795
+          <t>Record ID: KB_ROW_0142_0e8c8fcb6958
 Source Row ID: 142
-Company: Piedmont Automotive Products Inc.
+Company: piedmont automotive products inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Clarkesville, Habersham County
@@ -5012,7 +5012,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>KB_ROW_0143_72d4ff160943</t>
+          <t>KB_ROW_0143_f39466604579</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -5020,9 +5020,9 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0143_72d4ff160943
+          <t>Record ID: KB_ROW_0143_f39466604579
 Source Row ID: 143
-Company: PIOLAX Corp.
+Company: piolax corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Canton, Cherokee County
@@ -5044,7 +5044,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KB_ROW_0144_3ffda35c92da</t>
+          <t>KB_ROW_0144_a3587e59ec10</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5052,9 +5052,9 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0144_3ffda35c92da
+          <t>Record ID: KB_ROW_0144_a3587e59ec10
 Source Row ID: 144
-Company: Pirelli Tire North America LLC
+Company: pirelli tire north america llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Albany, Dougherty County
@@ -5076,7 +5076,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KB_ROW_0145_d0adbd896a2e</t>
+          <t>KB_ROW_0145_67836096c21a</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5084,9 +5084,9 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0145_d0adbd896a2e
+          <t>Record ID: KB_ROW_0145_67836096c21a
 Source Row ID: 145
-Company: Porsche Cars North America Inc.
+Company: porsche cars north america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
@@ -5108,7 +5108,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KB_ROW_0146_8bd980864111</t>
+          <t>KB_ROW_0146_5a8c6a78a653</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5116,9 +5116,9 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0146_8bd980864111
+          <t>Record ID: KB_ROW_0146_5a8c6a78a653
 Source Row ID: 146
-Company: PPG Industries Inc.
+Company: ppg industries inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Calhoun, Whitfield County
@@ -5140,7 +5140,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KB_ROW_0147_ed1a48cbba9e</t>
+          <t>KB_ROW_0147_5125d2107048</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5148,9 +5148,9 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0147_ed1a48cbba9e
+          <t>Record ID: KB_ROW_0147_5125d2107048
 Source Row ID: 147
-Company: Propex Operating Co. LLC
+Company: propex operating co. llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Pooler, Chatham County
@@ -5172,7 +5172,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KB_ROW_0148_14e000932e69</t>
+          <t>KB_ROW_0148_d70bda2b3a5a</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5180,9 +5180,9 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0148_14e000932e69
+          <t>Record ID: KB_ROW_0148_d70bda2b3a5a
 Source Row ID: 148
-Company: QSR Inc.
+Company: qsr inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Clayton County
@@ -5204,7 +5204,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KB_ROW_0149_bd8829101156</t>
+          <t>KB_ROW_0149_26e186c3a626</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -5212,9 +5212,9 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0149_bd8829101156
+          <t>Record ID: KB_ROW_0149_26e186c3a626
 Source Row ID: 149
-Company: Racemark International LLC
+Company: racemark international llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Gray, Jones County
@@ -5236,7 +5236,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KB_ROW_0150_d39e6495a1dc</t>
+          <t>KB_ROW_0150_5b4c1dbacbda</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -5244,9 +5244,9 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0150_d39e6495a1dc
+          <t>Record ID: KB_ROW_0150_5b4c1dbacbda
 Source Row ID: 150
-Company: RealTruck
+Company: realtruck
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Chattooga County
@@ -5268,7 +5268,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KB_ROW_0151_6a4ad90caea2</t>
+          <t>KB_ROW_0151_bf1a53f9dfbc</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -5276,9 +5276,9 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0151_6a4ad90caea2
+          <t>Record ID: KB_ROW_0151_bf1a53f9dfbc
 Source Row ID: 151
-Company: Rivian Automotive
+Company: rivian automotive
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
@@ -5300,7 +5300,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KB_ROW_0152_e087c1650b3a</t>
+          <t>KB_ROW_0152_00f083f9c97c</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -5308,9 +5308,9 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0152_e087c1650b3a
+          <t>Record ID: KB_ROW_0152_00f083f9c97c
 Source Row ID: 152
-Company: Robert Bosch LLC
+Company: robert bosch llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Flowery Branch, Gwinnett County
@@ -5332,7 +5332,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KB_ROW_0153_4d49580787d2</t>
+          <t>KB_ROW_0153_923482424b07</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -5340,9 +5340,9 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0153_4d49580787d2
+          <t>Record ID: KB_ROW_0153_923482424b07
 Source Row ID: 153
-Company: SAFT America Inc.
+Company: saft america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Cataula, Harris County
@@ -5364,7 +5364,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KB_ROW_0154_326c96a25af0</t>
+          <t>KB_ROW_0154_57ea64b26ef3</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -5372,9 +5372,9 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0154_326c96a25af0
+          <t>Record ID: KB_ROW_0154_57ea64b26ef3
 Source Row ID: 154
-Company: Sejong Georgia LLC
+Company: sejong georgia llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Jefferson, Jackson County
@@ -5396,7 +5396,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KB_ROW_0155_d3a6d0e4f61f</t>
+          <t>KB_ROW_0155_6afdf4d604b6</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -5404,9 +5404,9 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0155_d3a6d0e4f61f
+          <t>Record ID: KB_ROW_0155_6afdf4d604b6
 Source Row ID: 155
-Company: Seohan Auto USA
+Company: seohan auto usa
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Lamar County
@@ -5428,7 +5428,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KB_ROW_0156_808f18c530c5</t>
+          <t>KB_ROW_0156_499f002f62df</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5436,9 +5436,9 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0156_808f18c530c5
+          <t>Record ID: KB_ROW_0156_499f002f62df
 Source Row ID: 156
-Company: Seoyon E-HWA
+Company: seoyon e-hwa
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
@@ -5460,7 +5460,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KB_ROW_0157_a80d9cd16fe3</t>
+          <t>KB_ROW_0157_f76fbff8c113</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5468,9 +5468,9 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0157_a80d9cd16fe3
+          <t>Record ID: KB_ROW_0157_f76fbff8c113
 Source Row ID: 157
-Company: Seoyon E-Hwa Interior Systems
+Company: seoyon e-hwa interior systems
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
@@ -5492,7 +5492,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KB_ROW_0158_da87fe939de3</t>
+          <t>KB_ROW_0158_401f74d45630</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5500,9 +5500,9 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0158_da87fe939de3
+          <t>Record ID: KB_ROW_0158_401f74d45630
 Source Row ID: 158
-Company: Sewon America Inc.
+Company: sewon america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
@@ -5524,7 +5524,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KB_ROW_0159_9eec352a59cc</t>
+          <t>KB_ROW_0159_11bf33a1663b</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5532,9 +5532,9 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0159_9eec352a59cc
+          <t>Record ID: KB_ROW_0159_11bf33a1663b
 Source Row ID: 159
-Company: Sewon America Inc.
+Company: sewon america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
@@ -5556,7 +5556,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KB_ROW_0160_8aa1c1a52a6f</t>
+          <t>KB_ROW_0160_c85d8f15b0ad</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5564,9 +5564,9 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0160_8aa1c1a52a6f
+          <t>Record ID: KB_ROW_0160_c85d8f15b0ad
 Source Row ID: 160
-Company: Sewon America Inc.
+Company: sewon america inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
@@ -5588,7 +5588,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KB_ROW_0161_e2cf5c5ac0dc</t>
+          <t>KB_ROW_0161_96649d60f447</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -5596,9 +5596,9 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0161_e2cf5c5ac0dc
+          <t>Record ID: KB_ROW_0161_96649d60f447
 Source Row ID: 161
-Company: SHIROKI North America Inc
+Company: shiroki north america inc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Clayton County
@@ -5620,7 +5620,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KB_ROW_0162_d735a0aec5a1</t>
+          <t>KB_ROW_0162_abb104259149</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -5628,9 +5628,9 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0162_d735a0aec5a1
+          <t>Record ID: KB_ROW_0162_abb104259149
 Source Row ID: 162
-Company: SK Battery America
+Company: sk battery america
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Ellabell, Bryan County
@@ -5652,7 +5652,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KB_ROW_0163_e6a2a1f6acf8</t>
+          <t>KB_ROW_0163_292e5b57168f</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -5660,9 +5660,9 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0163_e6a2a1f6acf8
+          <t>Record ID: KB_ROW_0163_292e5b57168f
 Source Row ID: 163
-Company: SKF USA Inc.
+Company: skf usa inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Ringgold, Catoosa County
@@ -5684,7 +5684,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KB_ROW_0164_09240ba974d2</t>
+          <t>KB_ROW_0164_3b48b55133aa</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -5692,9 +5692,9 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0164_09240ba974d2
+          <t>Record ID: KB_ROW_0164_3b48b55133aa
 Source Row ID: 164
-Company: Solvay Specialty Polymers USA LLC
+Company: solvay specialty polymers usa llc
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Elbert County
@@ -5716,7 +5716,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KB_ROW_0165_62200285bb0a</t>
+          <t>KB_ROW_0165_cda00a5567e8</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -5724,9 +5724,9 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0165_62200285bb0a
+          <t>Record ID: KB_ROW_0165_cda00a5567e8
 Source Row ID: 165
-Company: Southern Switches Corp.
+Company: southern switches corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Dahlonega, Lumpkin County
@@ -5748,7 +5748,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KB_ROW_0166_ae288727aaef</t>
+          <t>KB_ROW_0166_5fcb6d22cfbd</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -5756,9 +5756,9 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0166_ae288727aaef
+          <t>Record ID: KB_ROW_0166_5fcb6d22cfbd
 Source Row ID: 166
-Company: SRG Global Inc.
+Company: srg global inc.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Covington, Newton County
@@ -5780,7 +5780,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KB_ROW_0167_38c97e41235b</t>
+          <t>KB_ROW_0167_06daad01bf4d</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -5788,9 +5788,9 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0167_38c97e41235b
+          <t>Record ID: KB_ROW_0167_06daad01bf4d
 Source Row ID: 167
-Company: Stryten Energy
+Company: stryten energy
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Alpharetta, Forsyth County
@@ -5812,7 +5812,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KB_ROW_0168_81a8154cea68</t>
+          <t>KB_ROW_0168_f72afc4ca381</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -5820,9 +5820,9 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0168_81a8154cea68
+          <t>Record ID: KB_ROW_0168_f72afc4ca381
 Source Row ID: 168
-Company: Suhner Manufacturing Corp.
+Company: suhner manufacturing corp.
 Category: Tier 1
 Industry Group: Transportation Equipment
 Updated Location: Rome, Floyd County
@@ -5844,7 +5844,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KB_ROW_0169_d1e6bb8df548</t>
+          <t>KB_ROW_0169_3a89873af3b5</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -5852,9 +5852,9 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0169_d1e6bb8df548
+          <t>Record ID: KB_ROW_0169_3a89873af3b5
 Source Row ID: 169
-Company: SungEel Recycling Park Georgia
+Company: sungeel recycling park georgia
 Category: Tier 2/3
 Industry Group: Miscellaneous Manufacturing Industries
 Updated Location: Duluth, Gwinnett County
@@ -5876,7 +5876,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KB_ROW_0170_d66f4308dbe2</t>
+          <t>KB_ROW_0170_9d1907602f95</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -5884,9 +5884,9 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0170_d66f4308dbe2
+          <t>Record ID: KB_ROW_0170_9d1907602f95
 Source Row ID: 170
-Company: Superior Essex Inc.
+Company: superior essex inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Kennesaw, Cobb County
@@ -5908,7 +5908,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KB_ROW_0171_39db23d47460</t>
+          <t>KB_ROW_0171_81f83c8a7d6f</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -5916,9 +5916,9 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0171_39db23d47460
+          <t>Record ID: KB_ROW_0171_81f83c8a7d6f
 Source Row ID: 171
-Company: Suzuki Manufacturing of America Corp.
+Company: suzuki manufacturing of america corp.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Rome, Douglas County
@@ -5940,7 +5940,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KB_ROW_0172_892105bb1129</t>
+          <t>KB_ROW_0172_ef160f501907</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -5948,9 +5948,9 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0172_892105bb1129
+          <t>Record ID: KB_ROW_0172_ef160f501907
 Source Row ID: 172
-Company: TCI Powder Coatings
+Company: tci powder coatings
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Ellaville, Schley County
@@ -5972,7 +5972,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KB_ROW_0173_897a6dfa5890</t>
+          <t>KB_ROW_0173_4359c912de52</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -5980,9 +5980,9 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0173_897a6dfa5890
+          <t>Record ID: KB_ROW_0173_4359c912de52
 Source Row ID: 173
-Company: TDK Components USA Inc.
+Company: tdk components usa inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Silver Creek, Floyd County
@@ -6004,7 +6004,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KB_ROW_0174_5d5313982545</t>
+          <t>KB_ROW_0174_86ebd01ccdb7</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -6012,9 +6012,9 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0174_5d5313982545
+          <t>Record ID: KB_ROW_0174_86ebd01ccdb7
 Source Row ID: 174
-Company: TE Connectivity
+Company: te connectivity
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Kennesaw, Cobb County
@@ -6036,7 +6036,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KB_ROW_0175_5bfaba53e516</t>
+          <t>KB_ROW_0175_71b207aa6d7a</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6044,9 +6044,9 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0175_5bfaba53e516
+          <t>Record ID: KB_ROW_0175_71b207aa6d7a
 Source Row ID: 175
-Company: Teklas USA
+Company: teklas usa
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Calhoun, Gordon County
@@ -6068,7 +6068,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KB_ROW_0176_4edb8803aa59</t>
+          <t>KB_ROW_0176_f328a9ee4f20</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -6076,9 +6076,9 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0176_4edb8803aa59
+          <t>Record ID: KB_ROW_0176_f328a9ee4f20
 Source Row ID: 176
-Company: Textron Specialized Vehicles
+Company: textron specialized vehicles
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Richmond County
@@ -6100,7 +6100,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KB_ROW_0177_49bcb1fa5464</t>
+          <t>KB_ROW_0177_86e3a6a070db</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -6108,9 +6108,9 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0177_49bcb1fa5464
+          <t>Record ID: KB_ROW_0177_86e3a6a070db
 Source Row ID: 177
-Company: Thermal Ceramics Inc.
+Company: thermal ceramics inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Richmond County
@@ -6132,7 +6132,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KB_ROW_0178_82ad92b2d092</t>
+          <t>KB_ROW_0178_d7b29ef83570</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -6140,9 +6140,9 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0178_82ad92b2d092
+          <t>Record ID: KB_ROW_0178_d7b29ef83570
 Source Row ID: 178
-Company: Thomson Plastics Inc.
+Company: thomson plastics inc.
 Category: OEM
 Industry Group: Transportation Equipment
 Updated Location: Monroe, Walton County
@@ -6164,7 +6164,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KB_ROW_0179_c07bfa883f66</t>
+          <t>KB_ROW_0179_96351daf0c51</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -6172,10 +6172,10 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0179_c07bfa883f66
+          <t>Record ID: KB_ROW_0179_96351daf0c51
 Source Row ID: 179
-Company: TI Fluid Systems
-Category: OEM (Footprint)
+Company: ti fluid systems
+Category: OEM Footprint
 Industry Group: Passenger vehicles (EV + ICE)
 Updated Location: Cartersville, Bartow County
 Address: 2 Swisher Dr, Cartersville, GA 30120
@@ -6186,7 +6186,7 @@
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 19600.0
-Product / Service: OEM footprint: Volvo passenger vehicles; NA operations footprint
+Product / Service: OEM footprint: Volvo passenger vehicles ; NA operations footprint
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 179</t>
@@ -6196,7 +6196,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KB_ROW_0180_37e7d866506a</t>
+          <t>KB_ROW_0180_188d364f2b96</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -6204,16 +6204,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0180_37e7d866506a
+          <t>Record ID: KB_ROW_0180_188d364f2b96
 Source Row ID: 180
-Company: TI Fluid Systems
+Company: ti fluid systems
 Category: OEM
 Industry Group: Automotive safety systems and restraints
 Updated Location: Cartersville, Bartow County
 Address: 2 Swisher Dr, Cartersville, GA 30120
 Latitude: 34.1446878814573
 Longitude: -84.7948577272343
-Primary Facility Type: Manufacturing / OEM operations
+Primary Facility Type: Manufacturing/ OEM operations
 EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE)
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
@@ -6228,7 +6228,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KB_ROW_0181_b96c2dee5ea7</t>
+          <t>KB_ROW_0181_215765048649</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -6236,10 +6236,10 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0181_b96c2dee5ea7
+          <t>Record ID: KB_ROW_0181_215765048649
 Source Row ID: 181
-Company: Tie Down Engineering
-Category: OEM (Footprint)
+Company: tie down engineering
+Category: OEM Footprint
 Industry Group: Heavy-duty trucks
 Updated Location: Atlanta, Fulton County
 Address: 605 Stonehill Dr SW, Atlanta, GA 30336
@@ -6260,7 +6260,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KB_ROW_0182_f772714b5fee</t>
+          <t>KB_ROW_0182_0d96b3ef16bf</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -6268,10 +6268,10 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0182_f772714b5fee
+          <t>Record ID: KB_ROW_0182_0d96b3ef16bf
 Source Row ID: 182
-Company: TN Americas Holding Inc.
-Category: OEM (Footprint)
+Company: tn americas holding inc.
+Category: OEM Footprint
 Industry Group: Commercial vehicles and powertrains
 Updated Location: Cumming, Forsyth County
 Address: 2200 Pendley Rd, Cumming, GA 30041
@@ -6282,7 +6282,7 @@
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 19600.0
-Product / Service: Commercial trucks (Volvo/Mack), buses, construction equipment; OEM footprint
+Product / Service: Commercial trucks (Volvo / Mack), buses, construction equipment ; OEM footprint
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 182</t>
@@ -6292,7 +6292,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KB_ROW_0183_5ac8be308ce4</t>
+          <t>KB_ROW_0183_eb5791ab8a54</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -6300,10 +6300,10 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0183_5ac8be308ce4
+          <t>Record ID: KB_ROW_0183_eb5791ab8a54
 Source Row ID: 183
-Company: Toyota Industries Group (TACG-TICA)
-Category: OEM (Footprint)
+Company: toyota industries group (tacg-tica)
+Category: OEM Footprint
 Industry Group: Commercial vehicles and powertrains
 Updated Location: Pendergrass, Jackson County
 Address: 1000 Valentine Industrial Pkwy, Pendergrass, GA 30567
@@ -6314,7 +6314,7 @@
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 18100.0
-Product / Service: Commercial trucks (Freightliner/Western Star) &amp; zero-emission truck programs
+Product / Service: Commercial trucks (Freightliner / Western Star) &amp; zero-emission truck programs
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 183</t>
@@ -6324,7 +6324,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KB_ROW_0184_f064c3c7f7d3</t>
+          <t>KB_ROW_0184_6153b57239d5</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -6332,10 +6332,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0184_f064c3c7f7d3
+          <t>Record ID: KB_ROW_0184_6153b57239d5
 Source Row ID: 184
-Company: Trenton Pressing
-Category: OEM (Footprint)
+Company: trenton pressing
+Category: OEM Footprint
 Industry Group: Commercial vehicles (Kenworth, Peterbilt)
 Updated Location: Trenton, Dade County
 Address: 505 N Industrial Blvd, Trenton, GA 30752
@@ -6346,7 +6346,7 @@
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 350.0
-Product / Service: Truck OEM footprint &amp; parts/distribution operations (PACCAR network)
+Product / Service: Truck OEM footprint &amp; parts / distribution operations (PACCAR network)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 184</t>
@@ -6356,7 +6356,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KB_ROW_0185_6530d82d0678</t>
+          <t>KB_ROW_0185_c460eb2cd154</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -6364,21 +6364,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0185_6530d82d0678
+          <t>Record ID: KB_ROW_0185_c460eb2cd154
 Source Row ID: 185
-Company: Trenton Pressing Inc.
+Company: trenton pressing inc.
 Category: OEM Supply Chain
 Industry Group: Automotive precision components
 Updated Location: Trenton, Dade County
 Address: 505 N Industrial Blvd, Trenton, GA 30752
 Latitude: 34.8787288016289
 Longitude: -85.497643922621
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Machined components supporting EV and ICE vehicles
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 298.0
-Product / Service: Precision-machined powertrain components (engine/transmission/drivetrain parts)
+Product / Service: Precision-machined powertrain components (engine / transmission / drivetrain parts)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 185</t>
@@ -6388,7 +6388,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KB_ROW_0186_38a7dbed516b</t>
+          <t>KB_ROW_0186_2e35d720d1f5</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -6396,21 +6396,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0186_38a7dbed516b
+          <t>Record ID: KB_ROW_0186_2e35d720d1f5
 Source Row ID: 186
-Company: Valeo
+Company: valeo
 Category: OEM Supply Chain
 Industry Group: Automotive parts manufacturing
 Updated Location: Unknown
 Address: Unknown
 Latitude: Unknown
 Longitude: Unknown
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Tier 1 automotive components
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 269.0
-Product / Service: Automotive body/stamped metal assemblies (Kia/Hyundai supply chain)
+Product / Service: Automotive body / stamped metal assemblies (Kia / Hyundai supply chain)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 186</t>
@@ -6420,7 +6420,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KB_ROW_0187_4f6c6a1e7500</t>
+          <t>KB_ROW_0187_c30711760533</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -6428,16 +6428,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0187_4f6c6a1e7500
+          <t>Record ID: KB_ROW_0187_c30711760533
 Source Row ID: 187
-Company: Vanguard National Trailer Corp.
+Company: vanguard national trailer corp.
 Category: OEM Supply Chain
 Industry Group: Automotive structural components
 Updated Location: Trenton, Dade County
 Address: 8 Vanguard Dr, Trenton, GA 30752
 Latitude: 34.886297855747
 Longitude: -85.496884427495
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Body and chassis components for EV and ICE OEMs
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
@@ -6452,7 +6452,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KB_ROW_0188_a59b04bf9496</t>
+          <t>KB_ROW_0188_79e988307663</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -6460,21 +6460,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0188_a59b04bf9496
+          <t>Record ID: KB_ROW_0188_79e988307663
 Source Row ID: 188
-Company: Vernay
+Company: vernay
 Category: OEM Supply Chain
 Industry Group: Automotive stamping and assemblies
 Updated Location: Griffin, Spalding County
 Address: 804 Greenbelt Pkwy, Griffin, GA 30223
 Latitude: 33.2377968959845
 Longitude: -84.2401653046223
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Stamped and welded assemblies for OEMs
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 1600.0
-Product / Service: Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)
+Product / Service: Automotive metal stamping &amp; body parts manufacturing (Hyundai / Kia supplier)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 188</t>
@@ -6484,7 +6484,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KB_ROW_0189_0de36736de86</t>
+          <t>KB_ROW_0189_a87d83aacdcb</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -6492,21 +6492,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0189_0de36736de86
+          <t>Record ID: KB_ROW_0189_a87d83aacdcb
 Source Row ID: 189
-Company: Vista Metals Corp.
+Company: vista metals corp.
 Category: OEM Supply Chain
 Industry Group: Automotive modules and components
 Updated Location: Adairsville, Bartow County
 Address: 800 Martin Luther King Jr Dr, Adairsville, GA 30103
 Latitude: 34.3676324336592
 Longitude: -84.9069879887994
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: EV and ICE component manufacturing
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 1500.0
-Product / Service: Automotive modules/powertrain components; parts supply
+Product / Service: Automotive modules / powertrain components ; parts supply
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 189</t>
@@ -6516,7 +6516,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>KB_ROW_0190_ab3ae9c0bb10</t>
+          <t>KB_ROW_0190_c206f9c99dda</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -6524,21 +6524,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0190_ab3ae9c0bb10
+          <t>Record ID: KB_ROW_0190_c206f9c99dda
 Source Row ID: 190
-Company: Voestalpine Automotive Body Parts Inc.
+Company: voestalpine automotive body parts inc.
 Category: OEM Supply Chain
 Industry Group: Automotive components
 Updated Location: Cartersville, Bartow County
 Address: 4334 Highway 20 SE, Cartersville, GA 30121
 Latitude: 34.181471
 Longitude: -84.738305
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: EV and ICE powertrain and HVAC components
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 1300.0
-Product / Service: Automotive components manufacturing group (compressors/automotive parts)
+Product / Service: Automotive components manufacturing group (compressors / automotive parts)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 190</t>
@@ -6548,7 +6548,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KB_ROW_0191_955802b6b8bc</t>
+          <t>KB_ROW_0191_afbcb949ba3c</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6556,21 +6556,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0191_955802b6b8bc
+          <t>Record ID: KB_ROW_0191_afbcb949ba3c
 Source Row ID: 191
-Company: Volvo Cars USA
+Company: volvo cars usa
 Category: OEM Supply Chain
 Industry Group: Automotive plastics
 Updated Location: Rabun County
 Address: 1800 Volvo Place, Mahwah, NJ 07430
 Latitude: 41.0740427635951
 Longitude: -74.1712478395491
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Plastic components for EV and ICE vehicles
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 456.0
-Product / Service: Automotive plastic parts manufacturing (interior/exterior components)
+Product / Service: Automotive plastic parts manufacturing (interior / exterior components)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 191</t>
@@ -6580,7 +6580,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>KB_ROW_0192_ea53e1e15dfd</t>
+          <t>KB_ROW_0192_ddb9bc62e79e</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -6588,21 +6588,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0192_ea53e1e15dfd
+          <t>Record ID: KB_ROW_0192_ddb9bc62e79e
 Source Row ID: 192
-Company: Volvo Group North America
+Company: volvo group north america
 Category: OEM Supply Chain
 Industry Group: Metal stamping and assemblies
 Updated Location: Lincoln County
 Address: 7900 National Service Rd, Greensboro, NC 27409
 Latitude: 36.0818642621738
 Longitude: -79.9684288843386
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Stamped metal components for OEMs
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 251.0
-Product / Service: Metal stamping/pressing for automotive components
+Product / Service: Metal stamping / pressing for automotive components
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 192</t>
@@ -6612,7 +6612,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KB_ROW_0193_c7374367639b</t>
+          <t>KB_ROW_0193_f8093fe34e01</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -6620,21 +6620,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0193_c7374367639b
+          <t>Record ID: KB_ROW_0193_f8093fe34e01
 Source Row ID: 193
-Company: Wabash National Corp.
+Company: wabash national corp.
 Category: OEM Supply Chain
 Industry Group: Automotive plastic components
 Updated Location: Ellenwood, Clayton County
 Address: 2620 Campbell Blvd, Ellenwood, GA 30294
 Latitude: 33.6209605672664
 Longitude: -84.3034983995488
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Interior and exterior plastic parts
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 20.0
-Product / Service: Automotive parts contract manufacturing (assemblies/components)
+Product / Service: Automotive parts contract manufacturing (assemblies / components)
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 193</t>
@@ -6644,7 +6644,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KB_ROW_0194_065ec8735c2d</t>
+          <t>KB_ROW_0194_abdec0a3bf97</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -6652,21 +6652,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0194_065ec8735c2d
+          <t>Record ID: KB_ROW_0194_abdec0a3bf97
 Source Row ID: 194
-Company: Wheelabrator Group Inc.
+Company: wheelabrator group inc.
 Category: OEM Supply Chain
 Industry Group: Automotive textiles and interiors
 Updated Location: LaGrange, Troup County
 Address: 1606 Executive Dr, LaGrange, GA 30240
 Latitude: 33.0087223514155
 Longitude: -85.0632892294943
-Primary Facility Type: Manufacturing plant
+Primary Facility Type: Manufacturing Plant
 EV Supply Chain Role: Interior trim and textile components
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 50.0
-Product / Service: Metal stamping &amp; fabrication for automotive/industrial components
+Product / Service: Metal stamping &amp; fabrication for automotive / industrial components
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 194</t>
@@ -6676,7 +6676,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KB_ROW_0195_a79f2371ca3f</t>
+          <t>KB_ROW_0195_093cbeb2825d</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -6684,21 +6684,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0195_a79f2371ca3f
+          <t>Record ID: KB_ROW_0195_093cbeb2825d
 Source Row ID: 195
-Company: WIKA USA
+Company: wika usa
 Category: OEM Supply Chain
 Industry Group: Automotive wiring systems
 Updated Location: Lawrenceville, Gwinnett County
 Address: 1000 Wiegand Blvd, Lawrenceville, GA 30043
 Latitude: 33.960968631134
 Longitude: -84.052709062173
-Primary Facility Type: Manufacturing / Engineering
+Primary Facility Type: Manufacturing/ Engineering
 EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 250000.0
-Product / Service: Vehicle power &amp; data solutions; wiring harnesses and connectors
+Product / Service: Vehicle power &amp; data solutions ; wiring harnesses and connectors
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 195</t>
@@ -6708,7 +6708,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>KB_ROW_0196_8ecedd8ffdcc</t>
+          <t>KB_ROW_0196_a54c741168c1</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -6716,9 +6716,9 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0196_8ecedd8ffdcc
+          <t>Record ID: KB_ROW_0196_a54c741168c1
 Source Row ID: 196
-Company: Woodbridge Foam Corp.
+Company: woodbridge foam corp.
 Category: OEM Supply Chain
 Industry Group: Automotive electrical systems
 Updated Location: Lithonia, DeKalb County
@@ -6740,7 +6740,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KB_ROW_0197_1cb842203027</t>
+          <t>KB_ROW_0197_8e04c110ab7a</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -6748,21 +6748,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0197_1cb842203027
+          <t>Record ID: KB_ROW_0197_8e04c110ab7a
 Source Row ID: 197
-Company: Woory Industrial Co.
+Company: woory industrial co.
 Category: OEM Supply Chain
 Industry Group: Electrical connectors and sensors
 Updated Location: Dublin, Laurens County
 Address: 404 Kellam Rd, Dublin, GA 31021
 Latitude: 32.5286348559853
 Longitude: -82.9311657105471
-Primary Facility Type: Manufacturing / Engineering
+Primary Facility Type: Manufacturing/ Engineering
 EV Supply Chain Role: High‑voltage EV connectors and electronics
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
 Employment: 87000.0
-Product / Service: Automotive connectors, terminals, sensors, and power/data components
+Product / Service: Automotive connectors, terminals, sensors, and power / data components
 EV / Battery Relevant: Yes
 Classification Method: Public OEM footprint / supplier listing
 Original Row ID: 197</t>
@@ -6772,7 +6772,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>KB_ROW_0198_7b64a7b43a26</t>
+          <t>KB_ROW_0198_95f76f62d8be</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -6780,9 +6780,9 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0198_7b64a7b43a26
+          <t>Record ID: KB_ROW_0198_95f76f62d8be
 Source Row ID: 198
-Company: Yachiyo Manufacturing of America LLC
+Company: yachiyo manufacturing of america llc
 Category: OEM Supply Chain
 Industry Group: Automotive seating and E‑systems
 Updated Location: Carrollton, Carroll County
@@ -6804,7 +6804,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>KB_ROW_0199_b8f4a37c78aa</t>
+          <t>KB_ROW_0199_2ee4c9fc6fdf</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -6812,16 +6812,16 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0199_b8f4a37c78aa
+          <t>Record ID: KB_ROW_0199_2ee4c9fc6fdf
 Source Row ID: 199
-Company: Yamaha Motor Manufacturing Corp.
+Company: yamaha motor manufacturing corp.
 Category: OEM Supply Chain
 Industry Group: Automotive electronics
 Updated Location: Newnan, Coweta County
 Address: 1000 Georgia Highway 34E, Newnan, GA
 Latitude: 33.4024771
 Longitude: -84.7323054
-Primary Facility Type: Engineering / Manufacturing
+Primary Facility Type: Engineering/ Manufacturing
 EV Supply Chain Role: Advanced electrical architecture for EVs
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
@@ -6836,7 +6836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>KB_ROW_0200_bf8bf88e6105</t>
+          <t>KB_ROW_0200_5de7be62f3e3</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -6844,16 +6844,16 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0200_bf8bf88e6105
+          <t>Record ID: KB_ROW_0200_5de7be62f3e3
 Source Row ID: 200
-Company: Yazaki North America
+Company: yazaki north america
 Category: OEM Footprint
 Industry Group: Automotive electronics and systems
 Updated Location: Spalding County
 Address: 375 Airport Rd, Griffin, Georgia
 Latitude: 33.2266019
 Longitude: -84.2867725
-Primary Facility Type: Engineering / Operations
+Primary Facility Type: Engineering/ Operations
 EV Supply Chain Role: Power electronics, sensors, and EV systems
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
@@ -6868,7 +6868,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>KB_ROW_0201_8aae30f43025</t>
+          <t>KB_ROW_0201_a58719044888</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -6876,16 +6876,16 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0201_8aae30f43025
+          <t>Record ID: KB_ROW_0201_a58719044888
 Source Row ID: 201
-Company: YKK USA Inc.
+Company: ykk usa inc.
 Category: OEM Footprint
 Industry Group: Automotive electronics and safety systems
 Updated Location: Marietta, Cobb County
 Address: 1300 Cobb Industrial Dr, Marietta, GA 30066
 Latitude: 33.9790253535143
 Longitude: -84.5308924242486
-Primary Facility Type: Engineering / Operations
+Primary Facility Type: Engineering/ Operations
 EV Supply Chain Role: EV sensors, braking, and control systems
 Primary OEMs: Unknown
 Supplier or Affiliation Type: Unknown
@@ -6900,7 +6900,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>KB_ROW_0202_fe091789b7c5</t>
+          <t>KB_ROW_0202_06b6128fab20</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -6908,9 +6908,9 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0202_fe091789b7c5
+          <t>Record ID: KB_ROW_0202_06b6128fab20
 Source Row ID: 202
-Company: ZF Gainesville LLC
+Company: zf gainesville llc
 Category: OEM Supply Chain
 Industry Group: Automotive systems and components
 Updated Location: Gainesville, Hall County
@@ -6932,7 +6932,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>KB_ROW_0203_9a54cf07dc7e</t>
+          <t>KB_ROW_0203_b78dea7ffaa1</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -6940,9 +6940,9 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0203_9a54cf07dc7e
+          <t>Record ID: KB_ROW_0203_b78dea7ffaa1
 Source Row ID: 203
-Company: ZF Gainesville LLC
+Company: zf gainesville llc
 Category: OEM Supply Chain
 Industry Group: Automotive thermal and electronics systems
 Updated Location: Gainesville, Hall County
@@ -6964,7 +6964,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>KB_ROW_0204_7fcf3e436be0</t>
+          <t>KB_ROW_0204_11aa7dfa2bd5</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -6972,9 +6972,9 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Record ID: KB_ROW_0204_7fcf3e436be0
+          <t>Record ID: KB_ROW_0204_11aa7dfa2bd5
 Source Row ID: 204
-Company: ZF Gainesville LLC
+Company: zf gainesville llc
 Category: OEM Footprint
 Industry Group: Automotive powertrain and thermal systems
 Updated Location: Gainesville, Hall County

--- a/georgia_ev_intelligence/outputs/parent_chunks.xlsx
+++ b/georgia_ev_intelligence/outputs/parent_chunks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,6 +448,7 @@
 Source Row ID: 0
 Company: acm georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: Warrenton, Warren County
 Address: 975 Thomson Hwy, Warrenton, GA 30828
@@ -480,6 +481,7 @@
 Source Row ID: 1
 Company: adient
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: West Point, Harris County
 Address: 1700 S Progress Pkwy, West Point, GA 31833
@@ -512,6 +514,7 @@
 Source Row ID: 2
 Company: advics manufacturing georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: LaGrange, Troup County
 Address: 1621 Lukken Industrial Dr W, LaGrange, GA 30240
@@ -544,6 +547,7 @@
 Source Row ID: 3
 Company: ajin georgia
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: Register, Bulloch County
 Address: 355 Rocky Rd, Register, GA 30452
@@ -576,6 +580,7 @@
 Source Row ID: 4
 Company: albaform inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: Flowery Branch, Hall County
 Address: 6505 McEver Rd, Flowery Branch, GA 30542
@@ -608,6 +613,7 @@
 Source Row ID: 5
 Company: anovion technologies
 Category: Tier 2/3
+State: Georgia
 Industry Group: Textile Products
 Updated Location: Bainbridge
 Address: Bainbridge, GA (street address not publicly confirmed)
@@ -640,6 +646,7 @@
 Source Row ID: 6
 Company: apache mills inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Paper and Allied Products
 Updated Location: Calhoun, Hall County
 Address: 3270 Joe Jerkins Blvd SE, Calhoun, GA 30701
@@ -672,6 +679,7 @@
 Source Row ID: 7
 Company: archer aviation inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Chemicals and Allied Products
 Updated Location: Covington, Morgan County
 Address: 2151 Centennial Pkwy NE, Covington, GA 30014
@@ -704,6 +712,7 @@
 Source Row ID: 8
 Company: arising industries inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Norcross, Gwinnett County
 Address: 6010 Unity Dr, Norcross, GA 30071
@@ -736,6 +745,7 @@
 Source Row ID: 9
 Company: arising industries inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Chemicals and Allied Products
 Updated Location: Norcross, Gwinnett County
 Address: 6010 Unity Dr, Norcross, GA 30071
@@ -768,6 +778,7 @@
 Source Row ID: 10
 Company: ascend elements
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Henry County
 Address: 1409 Brampton Ave, Covington, GA 30014
@@ -800,6 +811,7 @@
 Source Row ID: 11
 Company: aspen aerogels
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Statesboro
 Address: Statesboro, GA (planned plant—construction canceled)
@@ -832,6 +844,7 @@
 Source Row ID: 12
 Company: aurubis
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Augusta, Richmond County
 Address: 439 Valencia Way, Augusta, GA 30906
@@ -864,6 +877,7 @@
 Source Row ID: 13
 Company: avs
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Alpharetta, Forsyth County
 Address: 6110 McFarland Station Dr, Alpharetta, GA 30004
@@ -896,6 +910,7 @@
 Source Row ID: 14
 Company: beaver manufacturing co. inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Mansfield, Newton County
 Address: 12 Ed Needham Dr, Mansfield, GA 30055
@@ -928,6 +943,7 @@
 Source Row ID: 15
 Company: big tex trailer manufacturing inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Loganville, Gwinnett County
 Address: 3850 Harrison Rd, Loganville, GA 30052
@@ -960,6 +976,7 @@
 Source Row ID: 16
 Company: blue bird corp.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Fort Valley, Peach County
 Address: 402 Blue Bird Blvd, Fort Valley, GA 31030
@@ -992,6 +1009,7 @@
 Source Row ID: 17
 Company: blue ridge manufacturing
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Blue Ridge, Union County
 Address: 87 Tom Boyd Rd, Blue Ridge, GA 30513
@@ -1024,6 +1042,7 @@
 Source Row ID: 18
 Company: bonnell aluminum
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Newnan, Coweta County
 Address: 37 LaGrange St, Newnan, GA 30263
@@ -1056,6 +1075,7 @@
 Source Row ID: 19
 Company: boogook industries
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Macon, Bibb County
 Address: 2600 Weaver Rd Suite 1-11, Macon, GA 31217
@@ -1088,6 +1108,7 @@
 Source Row ID: 20
 Company: bosal industries georgia
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Lavonia, Franklin County
 Address: 1 Bosal Way, Lavonia, GA 30553
@@ -1120,6 +1141,7 @@
 Source Row ID: 21
 Company: bosch (automotive division)
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Toccoa, Stephens County
 Address: 1241 Meadowbrook Dr, Toccoa, GA 30577
@@ -1152,6 +1174,7 @@
 Source Row ID: 22
 Company: bridgestone bandag
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Griffin, Spalding County
 Address: 801 Greenbelt Pkwy, Griffin, GA 30223
@@ -1184,6 +1207,7 @@
 Source Row ID: 23
 Company: carcoustics usa
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Buford, Gwinnett County
 Address: 4740 S Lee St, Buford, GA 30518
@@ -1216,6 +1240,7 @@
 Source Row ID: 24
 Company: club car llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Evans, Columbia County
 Address: 4125 Washington Rd, Evans, GA 30809
@@ -1248,6 +1273,7 @@
 Source Row ID: 25
 Company: constellium automotive usa
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Cartersville, Bartow County
 Address: 1 Constellium Way, Cartersville, GA 30120
@@ -1280,6 +1306,7 @@
 Source Row ID: 26
 Company: continental automotive
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Fairburn, Fulton County
 Address: 7310 Oakley Industrial Blvd, Fairburn, GA 30213
@@ -1312,6 +1339,7 @@
 Source Row ID: 27
 Company: continental tire the americas llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Barnesville, Lamar County
 Address: 160 Aldora St, Barnesville, GA 30204
@@ -1344,6 +1372,7 @@
 Source Row ID: 28
 Company: daechang seat company
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Savannah, Chatham County
 Address: Savannah Chatham Manufacturing Center, Savannah, GA 31408
@@ -1376,6 +1405,7 @@
 Source Row ID: 29
 Company: daehan solution georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Henry County
 Address: 123 Industrial Blvd, Covington, GA 30014
@@ -1408,6 +1438,7 @@
 Source Row ID: 30
 Company: daesol ausys
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Smyrna, Cobb County
 Address: 2100 Lake Park Dr SE, Smyrna, GA 30080
@@ -1440,6 +1471,7 @@
 Source Row ID: 31
 Company: daesol material georgia, llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Duluth, Gwinnett County
 Address: 2895 Old Norcross Rd, Duluth, GA 30096
@@ -1472,6 +1504,7 @@
 Source Row ID: 32
 Company: daimler truck north america
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Covington, Newton County
 Address: 7400 E Freeman Pkwy, Covington, GA 30014
@@ -1504,6 +1537,7 @@
 Source Row ID: 33
 Company: das corp.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Metter, Candler County
 Address: 730 Fortner Rd, Metter, GA 30439
@@ -1536,6 +1570,7 @@
 Source Row ID: 34
 Company: decostar industries
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Buchanan, Polk County
 Address: 219 Evans Dr, Buchanan, GA 30113
@@ -1568,6 +1603,7 @@
 Source Row ID: 35
 Company: dekalb tool &amp; die inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Tucker, DeKalb County
 Address: 2220 Stephens Dr, Tucker, GA 30084
@@ -1600,6 +1636,7 @@
 Source Row ID: 36
 Company: denkai america
 Category: Tier 2/3
+State: Georgia
 Industry Group: Rubber and Miscellaneous Plastic Products
 Updated Location: Augusta, Richmond County
 Address: 1614 Douglas Rd, Augusta, GA 30906
@@ -1632,6 +1669,7 @@
 Source Row ID: 37
 Company: denso manufacturing georgia
 Category: Tier 2/3
+State: Georgia
 Industry Group: Stone, Clay, Glass and Concrete Products
 Updated Location: Pendergrass, Jackson County
 Address: 1000 Valentine Industrial Pkwy, Pendergrass, GA 30567
@@ -1664,6 +1702,7 @@
 Source Row ID: 38
 Company: die-tech industries inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Stone, Clay, Glass and Concrete Products
 Updated Location: Carrollton, Carroll County
 Address: 102 Automation Dr, Carrollton, GA 30117
@@ -1696,6 +1735,7 @@
 Source Row ID: 39
 Company: dinex emissions inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Dublin, Laurens County
 Address: 2020 Waldrep Industrial Blvd., Dublin, GA 31021
@@ -1728,6 +1768,7 @@
 Source Row ID: 40
 Company: dongwon autopart technology georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Hogansville, Meriwether County
 Address: 475 Meriwether Park Dr, Hogansville, GA 30230
@@ -1760,6 +1801,7 @@
 Source Row ID: 41
 Company: dorsett industries inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Dalton, Whitfield County
 Address: 1304 May Street, Dalton, GA 30721
@@ -1792,6 +1834,7 @@
 Source Row ID: 42
 Company: down 2 earth trailers
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Baxley, Appling County
 Address: 1605 E Parker Street, Baxley, GA 31513
@@ -1824,6 +1867,7 @@
 Source Row ID: 43
 Company: duckyang
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Braselton, Jackson County
 Address: 984 Broadway Avenue, Braselton, GA 30517
@@ -1856,6 +1900,7 @@
 Source Row ID: 44
 Company: eaton corp.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Athens, Clarke County
 Address: 695 Indian Hills Road, Athens, GA 30601
@@ -1888,6 +1933,7 @@
 Source Row ID: 45
 Company: ecoplastic america corporation
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Register, Bulloch County
 Address: 4800 Highway 301 S., Register, GA 30452
@@ -1920,6 +1966,7 @@
 Source Row ID: 46
 Company: ecoplastic corporation
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Statesboro, Bulloch County
 Address: 25 Siebald St, Statesboro, GA 30458
@@ -1952,6 +1999,7 @@
 Source Row ID: 47
 Company: elan technology inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Midway, Liberty County
 Address: 169 Elan Court, Midway, GA 31320
@@ -1984,6 +2032,7 @@
 Source Row ID: 48
 Company: enchem america inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Commerce, Jackson County
 Address: 648 Highway 334, Commerce, GA 30530
@@ -2016,6 +2065,7 @@
 Source Row ID: 49
 Company: enplas usa inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Marietta, Cobb County
 Address: 1901 West Oak Circle, Marietta, GA 30062
@@ -2048,6 +2098,7 @@
 Source Row ID: 50
 Company: erdrich usa inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Dublin, Laurens County
 Address: 112 Willie Paulk Parkway, Dublin, GA 31021
@@ -2080,6 +2131,7 @@
 Source Row ID: 51
 Company: evco plastics
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Calhoun, Gordon County
 Address: 100 EVCO Drive, Calhoun, GA 30701
@@ -2112,6 +2164,7 @@
 Source Row ID: 52
 Company: f&amp;p georgia manufacturing
 Category: Tier 1/2
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Rome, Floyd County
 Address: 88 Enterprise Drive SE, Rome, GA 30161
@@ -2144,6 +2197,7 @@
 Source Row ID: 53
 Company: fanello industries inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Lavonia, Franklin County
 Address: 50 E Main Street, Lavonia, GA 30553
@@ -2176,6 +2230,7 @@
 Source Row ID: 54
 Company: first american resources
 Category: Tier 2/3
+State: Georgia
 Industry Group: Primary Metal Industries
 Updated Location: Mableton, Cobb County
 Address: 2030 Riverview Industrial Dr SE, Mableton, GA 30126
@@ -2208,6 +2263,7 @@
 Source Row ID: 55
 Company: flambeau inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Madison, Morgan County
 Address: 1330 Atlanta Highway, Madison, GA 30650
@@ -2240,6 +2296,7 @@
 Source Row ID: 56
 Company: fouts brothers fire equipment
 Category: Tier 1/2
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Milledgeville, Baldwin County
 Address: 138 Roberson Mill Rd, Milledgeville, GA 31061
@@ -2272,6 +2329,7 @@
 Source Row ID: 57
 Company: fox factory
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Duluth, Gwinnett County
 Address: 2055 Sugarloaf Circle, Suite 300, Duluth, GA 30097
@@ -2304,6 +2362,7 @@
 Source Row ID: 58
 Company: freudenberg-nok
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: LaGrange, Troup County
 Address: 1618 Lukken Industrial Dr, LaGrange, GA 30240
@@ -2336,6 +2395,7 @@
 Source Row ID: 59
 Company: freudenberg-nok
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: LaGrange, Troup County
 Address: 1618 Lukken Industrial Dr, LaGrange, GA 30240
@@ -2368,6 +2428,7 @@
 Source Row ID: 60
 Company: freyr battery
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Atlanta, Fulton County
 Address: 601 10th St NW, Suite 400, Atlanta, GA 30318
@@ -2400,6 +2461,7 @@
 Source Row ID: 61
 Company: gedia georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Dalton, Fulton County
 Address: 1 GEDIA Way, Dalton, GA 30721
@@ -2432,6 +2494,7 @@
 Source Row ID: 62
 Company: global powertrain systems llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Jefferson, Jackson County
 Address: 300 Logistics Parkway, Jefferson, GA 30549
@@ -2464,6 +2527,7 @@
 Source Row ID: 63
 Company: glovis georgia llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
 Address: 127 N Park Ct, Savannah, GA 31407
@@ -2496,6 +2560,7 @@
 Source Row ID: 64
 Company: goodyear tire &amp; rubber co.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Atlanta, Clayton County
 Address: 1420 Phoenix Blvd, Suite 300, Atlanta, GA 30349
@@ -2528,6 +2593,7 @@
 Source Row ID: 65
 Company: great dane lp
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
 Address: 602 E Lathrop Ave, Savannah, GA 31415
@@ -2560,6 +2626,7 @@
 Source Row ID: 66
 Company: great dane trailers
 Category: Tier 2/3
+State: Georgia
 Industry Group: Fabricated Metal Products
 Updated Location: Savannah, Chatham County
 Address: 602 E Lathrop Ave, Savannah, GA 31415
@@ -2592,6 +2659,7 @@
 Source Row ID: 67
 Company: grudem
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Gainesville, Hall County
 Address: 1245 Industrial Blvd, Gainesville, GA 30501
@@ -2624,6 +2692,7 @@
 Source Row ID: 68
 Company: gsc steel stamping llc
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Adairsville, Bartow County
 Address: 104 International Pkwy, Adairsville, GA 30103
@@ -2656,6 +2725,7 @@
 Source Row ID: 69
 Company: haering precision usa lp
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Buford, Hall County
 Address: 5000 Frontage Rd, Buford, GA 30518
@@ -2688,6 +2758,7 @@
 Source Row ID: 70
 Company: haering precision usa lp
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Buford, Hall County
 Address: 5000 Frontage Rd, Buford, GA 30518
@@ -2720,6 +2791,7 @@
 Source Row ID: 71
 Company: hanon systems usa llc
 Category: Tier 2/3
+State: Alabama
 Industry Group: Machinery Except Electrical
 Updated Location: Shorter, Harris County
 Address: 400 Hanon Dr, Shorter, GA 36075
@@ -2752,6 +2824,7 @@
 Source Row ID: 72
 Company: hella automotive sales inc.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Atlanta, Cobb County
 Address: 2018 Powers Ferry Rd SE, Suite 400, Atlanta, GA 30339
@@ -2784,6 +2857,7 @@
 Source Row ID: 73
 Company: hexpol compounding corp.
 Category: Tier 2/3
+State: Georgia
 Industry Group: Machinery Except Electrical
 Updated Location: Griffin, Spalding County
 Address: 1020 Plantation Way, Griffin, GA 30224
@@ -2816,6 +2890,7 @@
 Source Row ID: 74
 Company: hitachi astemo
 Category: Tier 1/2
+State: Alabama
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Shorter, Harris County
 Address: 400 Hanon Dr, Shorter, GA 36075
@@ -2848,6 +2923,7 @@
 Source Row ID: 75
 Company: hitachi astemo americas inc.
 Category: Tier 1/2
+State: Alabama
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Shorter, Harris County
 Address: 400 Hanon Dr, Shorter, GA 36075
@@ -2880,6 +2956,7 @@
 Source Row ID: 76
 Company: hollingsworth &amp; vose co.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Hawkinsville, Pulaski County
 Address: 111 Hollingsworth &amp; Vose Rd, Hawkinsville, GA 31036
@@ -2912,6 +2989,7 @@
 Source Row ID: 77
 Company: honda development &amp; manufacturing
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Tallapoosa, Cherokee County
 Address: 1000 Honda Dr, Tallapoosa, GA 30176
@@ -2944,6 +3022,7 @@
 Source Row ID: 78
 Company: hwashin
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: LaGrange, Haralson County
 Address: 1465 Troup Industrial Blvd, LaGrange, GA 30240
@@ -2976,6 +3055,7 @@
 Source Row ID: 79
 Company: hyundai &amp; lg energy solution (lges)
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Chatham County
 Address: 700 Hyundai Blvd, Ellabell, GA 31308
@@ -3008,6 +3088,7 @@
 Source Row ID: 80
 Company: hyundai industrial co.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Chatham County
 Address: 700 Hyundai Blvd, Ellabell, GA 31308
@@ -3040,6 +3121,7 @@
 Source Row ID: 81
 Company: hyundai mobis (georgia)
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
 Address: 300 Hyundai MOBIS Dr, West Point, GA 31833
@@ -3072,6 +3154,7 @@
 Source Row ID: 82
 Company: hyundai motor group
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Ellabell, Bryan County
 Address: 700 Hyundai Blvd, Ellabell, GA 31308
@@ -3104,6 +3187,7 @@
 Source Row ID: 83
 Company: hyundai transys georgia powertrain
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
 Address: 100 Powertrain Way, West Point, GA 31833
@@ -3136,6 +3220,7 @@
 Source Row ID: 84
 Company: hyundai transys georgia seating systems
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: West Point, Troup County
 Address: 801 Transys Pkwy, West Point, GA 31833
@@ -3168,6 +3253,7 @@
 Source Row ID: 85
 Company: immi
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Dublin, Laurens County
 Address: 2002 Industrial Park Dr, Dublin, GA 31021
@@ -3200,6 +3286,7 @@
 Source Row ID: 86
 Company: ims gear georgia inc.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Suwanee, Gwinnett County
 Address: 300 Satellite Blvd NE, Suwanee, GA 30024
@@ -3232,6 +3319,7 @@
 Source Row ID: 87
 Company: inalfa roof systems inc.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Acworth, Cobb County
 Address: 100 Inalfa Dr, Acworth, GA 30102
@@ -3264,6 +3352,7 @@
 Source Row ID: 88
 Company: jac products inc.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Jefferson, Jackson County
 Address: 120 Logistics Pkwy, Jefferson, GA 30549
@@ -3296,6 +3385,7 @@
 Source Row ID: 89
 Company: jefferson southern corp.
 Category: Tier 1/2
+State: Georgia
 Industry Group: Electronic and Other Electrical Equipment and Components
 Updated Location: Commerce, Forsyth County
 Address: 1 Jefferson Southern Dr, Commerce, GA 30529
@@ -3328,6 +3418,7 @@
 Source Row ID: 90
 Company: jefferson southern corporation
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Commerce, Forsyth County
 Address: 1 Jefferson Southern Dr, Commerce, GA 30529
@@ -3360,6 +3451,7 @@
 Source Row ID: 91
 Company: joon georgia, inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Chattahoochee County
 Address: 100 Industrial Park Rd, West Point, GA 31833
@@ -3392,6 +3484,7 @@
 Source Row ID: 92
 Company: jtekt north america corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Pendergrass, Jackson County
 Address: 301 Teco Dr, Pendergrass, GA 30567
@@ -3424,6 +3517,7 @@
 Source Row ID: 93
 Company: kautex inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Lavonia, Rabun County
 Address: 100 Kautex Dr, Lavonia, GA 30553
@@ -3456,6 +3550,7 @@
 Source Row ID: 94
 Company: kia georgia inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
 Address: 1025 Kia Blvd, West Point, GA 31833
@@ -3488,6 +3583,7 @@
 Source Row ID: 95
 Company: ktx america corporation
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Meriwether County
 Address: 205 KTX Dr, LaGrange, GA 30240
@@ -3520,6 +3616,7 @@
 Source Row ID: 96
 Company: kumho tire usa inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Macon, Bibb County
 Address: 1 Kumho Dr, Macon, GA 31216
@@ -3552,6 +3649,7 @@
 Source Row ID: 97
 Company: kyungshin america corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
 Address: 85 Kyungshin Dr, West Point, GA 31833
@@ -3584,6 +3682,7 @@
 Source Row ID: 98
 Company: lark united manufacturing inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Laurens County
 Address: 200 Industrial Blvd, Dublin, GA 31021
@@ -3616,6 +3715,7 @@
 Source Row ID: 99
 Company: lear corporation
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Hammond Industrial Park, Troup County
 Address: 100 Lear Dr, Hammond Industrial Park, GA 30240
@@ -3648,6 +3748,7 @@
 Source Row ID: 100
 Company: lehigh technologies inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Tucker, Walton County
 Address: 1000 New Horizons Way, Tucker, GA 30084
@@ -3680,6 +3781,7 @@
 Source Row ID: 101
 Company: linde + wiemann
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Laurens County
 Address: 200 Linde Wiemann Way, Dublin, GA 31021
@@ -3712,6 +3814,7 @@
 Source Row ID: 102
 Company: lund international inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Madison, Morgan County
 Address: 189 Excalibur Dr, Madison, GA 30650
@@ -3744,6 +3847,7 @@
 Source Row ID: 103
 Company: lund international inc./ventshade division
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Madison, Morgan County
 Address: 189 Excalibur Dr, Madison, GA 30650
@@ -3776,6 +3880,7 @@
 Source Row ID: 104
 Company: lyle industries inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dawsonville, Dawson County
 Address: 715 Lyle Industrial Dr, Dawsonville, GA 30534
@@ -3808,6 +3913,7 @@
 Source Row ID: 105
 Company: lyle industries inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dawsonville, Dawson County
 Address: 715 Lyle Industrial Dr, Dawsonville, GA 30534
@@ -3840,6 +3946,7 @@
 Source Row ID: 106
 Company: mack trucks
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dublin, Lowndes County
 Address: 1525 Madison Hwy, Dublin, GA 31021
@@ -3872,6 +3979,7 @@
 Source Row ID: 107
 Company: magna international
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Carrollton, Carroll County
 Address: 250 Magna Dr, Carrollton, GA 30117
@@ -3904,6 +4012,7 @@
 Source Row ID: 108
 Company: mando america corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Hogansville, Meriwether County
 Address: 100 Mando Dr, Hogansville, GA 30230
@@ -3936,6 +4045,7 @@
 Source Row ID: 109
 Company: master craft engineering inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Lavonia, Franklin County
 Address: 1000 Mastercraft Ln, Lavonia, GA 30553
@@ -3968,6 +4078,7 @@
 Source Row ID: 110
 Company: mat heavy duty
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Gwinnett County
 Address: 555 Satellite Blvd NW, Suwanee, GA 30024
@@ -4000,6 +4111,7 @@
 Source Row ID: 111
 Company: maxxis international usa
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Clayton County
 Address: 100 International Pkwy, Suwanee, GA 30024
@@ -4032,6 +4144,7 @@
 Source Row ID: 112
 Company: mercedes-benz usa llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Sandy Springs, Fulton County
 Address: 1 Mercedes-Benz Dr, Sandy Springs, GA 30328
@@ -4064,6 +4177,7 @@
 Source Row ID: 113
 Company: michelin tread technologies
 Category: Tier 1
+State: South Carolina
 Industry Group: Transportation Equipment
 Updated Location: Hart County
 Address: 1 Parkway South Blvd, Greenville, SC 29615
@@ -4096,6 +4210,7 @@
 Source Row ID: 114
 Company: milliken &amp; co./valway plant
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
 Address: 920 Milliken Rd, LaGrange, GA 30241
@@ -4128,6 +4243,7 @@
 Source Row ID: 115
 Company: minebea accesssolutions usa inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Gainesville, Fulton County
 Address: 200 Access Way, Gainesville, GA 30501
@@ -4160,6 +4276,7 @@
 Source Row ID: 116
 Company: mobis alabama llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
 Address: 300 Hyundai MOBIS Dr, West Point, GA 31833
@@ -4192,6 +4309,7 @@
 Source Row ID: 117
 Company: mollertech llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dalton, Whitfield County
 Address: 100 Mollertech Dr, Dalton, GA 30721
@@ -4224,6 +4342,7 @@
 Source Row ID: 118
 Company: morgan corp.
 Category: Tier 1
+State: North Carolina
 Industry Group: Transportation Equipment
 Updated Location: Rabun County
 Address: 15 Morgan Center Dr, Morganton, NC 28655
@@ -4256,6 +4375,7 @@
 Source Row ID: 119
 Company: murata electronics north america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Smyrna, Paulding County
 Address: 1000 Corporate Dr, Smyrna, GA 30080
@@ -4288,6 +4408,7 @@
 Source Row ID: 120
 Company: neaton rome inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Rome, Douglas County
 Address: 1 Neaton Dr, Rome, GA 30161
@@ -4320,6 +4441,7 @@
 Source Row ID: 121
 Company: nidec elesys americas corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Forsyth County
 Address: 3900 Lakefield Ct, Suwanee, GA 30024
@@ -4352,6 +4474,7 @@
 Source Row ID: 122
 Company: nifco ktw america corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Toccoa, Stephens County
 Address: 100 Nifco Way, Toccoa, GA 30577
@@ -4384,6 +4507,7 @@
 Source Row ID: 123
 Company: nile automotive
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Cumming, Forsyth County
 Address: 4490 Alicia Lane, Cumming, GA 30028
@@ -4416,6 +4540,7 @@
 Source Row ID: 124
 Company: nisshinbo automotive manufacturing inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Covington, Newton County
 Address: 14187 Nisshinbo Drive, Covington, GA 30014
@@ -4448,6 +4573,7 @@
 Source Row ID: 125
 Company: nivel parts &amp; manufacturing co. llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Cairo, Grady County
 Address: 2051 2nd Ave NE, Cairo, GA 39828
@@ -4480,6 +4606,7 @@
 Source Row ID: 126
 Company: novelis inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
 Address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
@@ -4512,6 +4639,7 @@
 Source Row ID: 127
 Company: novelis inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
 Address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
@@ -4544,6 +4672,7 @@
 Source Row ID: 128
 Company: novelis inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
 Address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
@@ -4576,6 +4705,7 @@
 Source Row ID: 129
 Company: nvh korea
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Locust Grove, Henry County
 Address: 120 Colvin Drive, Locust Grove, GA 30248
@@ -4608,6 +4738,7 @@
 Source Row ID: 130
 Company: oneda corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Gainesville, Hall County
 Address: 2157 Atlanta Highway, Gainesville, GA 30504
@@ -4640,6 +4771,7 @@
 Source Row ID: 131
 Company: otr wheel engineering inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Rome, Floyd County
 Address: 6 Riverside Industrial Park, Rome, GA 30161
@@ -4672,6 +4804,7 @@
 Source Row ID: 132
 Company: paccar
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Morrow, Clayton County
 Address: 6853 Southlake Pkwy, Morrow, GA 30260
@@ -4704,6 +4837,7 @@
 Source Row ID: 133
 Company: pai industries inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Mableton, Cobb County
 Address: 2125 Clay Drive, Mableton, GA 30126
@@ -4736,6 +4870,7 @@
 Source Row ID: 134
 Company: pak-lite inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Suwanee, Gwinnett County
 Address: 550 Old Peachtree Rd NW, Suwanee, GA 30024
@@ -4768,6 +4903,7 @@
 Source Row ID: 135
 Company: panasonic automotive systems co.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Fayette County
 Address: 1 Panasonic Way, Peachtree City, GA 30269
@@ -4800,6 +4936,7 @@
 Source Row ID: 136
 Company: panasonic automotive systems co.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Fayette County
 Address: 1 Panasonic Way, Peachtree City, GA 30269
@@ -4832,6 +4969,7 @@
 Source Row ID: 137
 Company: panduit corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Cumming, Forsyth County
 Address: 1819 Atlanta Hwy, Cumming, GA 30040
@@ -4864,6 +5002,7 @@
 Source Row ID: 138
 Company: peerless-winsmith inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Flowery Branch, Hall County
 Address: 4510 Cantrell Road, Flowery Branch, GA 30542
@@ -4896,6 +5035,7 @@
 Source Row ID: 139
 Company: perkins small engines llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Griffin, Spalding County
 Address: 325 Green Valley Road, Griffin, GA 30224
@@ -4928,6 +5068,7 @@
 Source Row ID: 140
 Company: peterson spring
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Athens, Clarke County
 Address: 600 Old Hull Road, Athens, GA 30601
@@ -4960,6 +5101,7 @@
 Source Row ID: 141
 Company: pha body systems llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Bloomingdale, Chatham County
 Address: 300 Monahan Drive, Bloomingdale, GA 31302
@@ -4992,6 +5134,7 @@
 Source Row ID: 142
 Company: piedmont automotive products inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Clarkesville, Habersham County
 Address: 1058 Rocky Branch Rd, Clarkesville, GA 30523
@@ -5024,6 +5167,7 @@
 Source Row ID: 143
 Company: piolax corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Canton, Cherokee County
 Address: 139 Etowah Industrial Court, Canton, GA 30114
@@ -5056,6 +5200,7 @@
 Source Row ID: 144
 Company: pirelli tire north america llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Albany, Dougherty County
 Address: 2819 Old Dawson Rd, Albany, GA 31707
@@ -5088,6 +5233,7 @@
 Source Row ID: 145
 Company: porsche cars north america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
 Address: 1 Porsche Dr, Atlanta, GA 30328
@@ -5120,6 +5266,7 @@
 Source Row ID: 146
 Company: ppg industries inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Calhoun, Whitfield County
 Address: 500 Enterprise Dr, Calhoun, GA 30701
@@ -5152,6 +5299,7 @@
 Source Row ID: 147
 Company: propex operating co. llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Pooler, Chatham County
 Address: 490 Chatham Pkwy, Pooler, GA 31322
@@ -5184,6 +5332,7 @@
 Source Row ID: 148
 Company: qsr inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Clayton County
 Address: 135 QSR Rd, LaGrange, GA 30240
@@ -5216,6 +5365,7 @@
 Source Row ID: 149
 Company: racemark international llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Gray, Jones County
 Address: 152 Racemark Dr, Gray, GA 31032
@@ -5248,6 +5398,7 @@
 Source Row ID: 150
 Company: realtruck
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Peachtree City, Chattooga County
 Address: 1656 Airport Rd N, Peachtree City, GA 30269
@@ -5280,6 +5431,7 @@
 Source Row ID: 151
 Company: rivian automotive
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Atlanta, Fulton County
 Address: 1090 Roberts Dr NW, Atlanta, GA 30318
@@ -5312,6 +5464,7 @@
 Source Row ID: 152
 Company: robert bosch llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Flowery Branch, Gwinnett County
 Address: 6330 W Broad St, Flowery Branch, GA 30542
@@ -5344,6 +5497,7 @@
 Source Row ID: 153
 Company: saft america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Cataula, Harris County
 Address: 15621 Hopewell Church Rd, Cataula, GA 31804
@@ -5376,6 +5530,7 @@
 Source Row ID: 154
 Company: sejong georgia llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Jefferson, Jackson County
 Address: 100 Sejong Way, Jefferson, GA 30549
@@ -5408,6 +5563,7 @@
 Source Row ID: 155
 Company: seohan auto usa
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Lamar County
 Address: 850 Lamar St, LaGrange, GA 30240
@@ -5440,6 +5596,7 @@
 Source Row ID: 156
 Company: seoyon e-hwa
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
 Address: 200 Seoyon E-HWA Blvd, West Point, GA 31833
@@ -5472,6 +5629,7 @@
 Source Row ID: 157
 Company: seoyon e-hwa interior systems
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: West Point, Troup County
 Address: 200 Seoyon E-HWA Blvd, West Point, GA 31833
@@ -5504,6 +5662,7 @@
 Source Row ID: 158
 Company: sewon america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
 Address: 210 Sewon Dr, LaGrange, GA 30241
@@ -5536,6 +5695,7 @@
 Source Row ID: 159
 Company: sewon america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
 Address: 210 Sewon Dr, LaGrange, GA 30241
@@ -5568,6 +5728,7 @@
 Source Row ID: 160
 Company: sewon america inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Troup County
 Address: 210 Sewon Dr, LaGrange, GA 30241
@@ -5600,6 +5761,7 @@
 Source Row ID: 161
 Company: shiroki north america inc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: LaGrange, Clayton County
 Address: 100 Shiroki Way, LaGrange, GA 30241
@@ -5632,6 +5794,7 @@
 Source Row ID: 162
 Company: sk battery america
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Ellabell, Bryan County
 Address: 700 Hyundai Blvd, Ellabell, GA 31308
@@ -5664,6 +5827,7 @@
 Source Row ID: 163
 Company: skf usa inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Ringgold, Catoosa County
 Address: 301 David Fletcher Dr, Ringgold, GA 30736
@@ -5696,6 +5860,7 @@
 Source Row ID: 164
 Company: solvay specialty polymers usa llc
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Elbert County
 Address: 600 Patterson Ave, Augusta, GA 30901
@@ -5728,6 +5893,7 @@
 Source Row ID: 165
 Company: southern switches corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Dahlonega, Lumpkin County
 Address: 715 Happy Hollow Rd, Dahlonega, GA 30533
@@ -5760,6 +5926,7 @@
 Source Row ID: 166
 Company: srg global inc.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Covington, Newton County
 Address: 10116 Industrial Blvd NE, Covington, GA 30014
@@ -5792,6 +5959,7 @@
 Source Row ID: 167
 Company: stryten energy
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Alpharetta, Forsyth County
 Address: 5925 Cabot Pkwy, Alpharetta, GA 30005
@@ -5824,6 +5992,7 @@
 Source Row ID: 168
 Company: suhner manufacturing corp.
 Category: Tier 1
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Rome, Floyd County
 Address: 43 Anderson Rd SW, Rome, GA 30161
@@ -5856,6 +6025,7 @@
 Source Row ID: 169
 Company: sungeel recycling park georgia
 Category: Tier 2/3
+State: Georgia
 Industry Group: Miscellaneous Manufacturing Industries
 Updated Location: Duluth, Gwinnett County
 Address: 3237 Satellite Blvd, Suite 175, Duluth, GA 30096
@@ -5888,6 +6058,7 @@
 Source Row ID: 170
 Company: superior essex inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Kennesaw, Cobb County
 Address: 3600 Cobb International Blvd NW, Kennesaw, GA 30152
@@ -5920,6 +6091,7 @@
 Source Row ID: 171
 Company: suzuki manufacturing of america corp.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Rome, Douglas County
 Address: 1000 McIntosh Trail SW, Rome, GA 30165
@@ -5952,6 +6124,7 @@
 Source Row ID: 172
 Company: tci powder coatings
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Ellaville, Schley County
 Address: 610 Dixon Dr, Ellaville, GA 31806
@@ -5984,6 +6157,7 @@
 Source Row ID: 173
 Company: tdk components usa inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Silver Creek, Floyd County
 Address: 4058 Rockmart Rd, Silver Creek, GA 30173
@@ -6016,6 +6190,7 @@
 Source Row ID: 174
 Company: te connectivity
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Kennesaw, Cobb County
 Address: 3295 Cobb International Blvd NW, Kennesaw, GA 30152
@@ -6048,6 +6223,7 @@
 Source Row ID: 175
 Company: teklas usa
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Calhoun, Gordon County
 Address: 320 S Industrial Blvd, Calhoun, GA 30701
@@ -6080,6 +6256,7 @@
 Source Row ID: 176
 Company: textron specialized vehicles
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Richmond County
 Address: 1451 Marvin Griffin Rd, Augusta, GA 30906
@@ -6112,6 +6289,7 @@
 Source Row ID: 177
 Company: thermal ceramics inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Augusta, Richmond County
 Address: 2190 N Leg Rd, Augusta, GA 30909
@@ -6144,6 +6322,7 @@
 Source Row ID: 178
 Company: thomson plastics inc.
 Category: OEM
+State: Georgia
 Industry Group: Transportation Equipment
 Updated Location: Monroe, Walton County
 Address: 1440 H D Atha Rd, Monroe, GA 30656
@@ -6176,6 +6355,7 @@
 Source Row ID: 179
 Company: ti fluid systems
 Category: OEM Footprint
+State: Georgia
 Industry Group: Passenger vehicles (EV + ICE)
 Updated Location: Cartersville, Bartow County
 Address: 2 Swisher Dr, Cartersville, GA 30120
@@ -6208,6 +6388,7 @@
 Source Row ID: 180
 Company: ti fluid systems
 Category: OEM
+State: Georgia
 Industry Group: Automotive safety systems and restraints
 Updated Location: Cartersville, Bartow County
 Address: 2 Swisher Dr, Cartersville, GA 30120
@@ -6240,6 +6421,7 @@
 Source Row ID: 181
 Company: tie down engineering
 Category: OEM Footprint
+State: Georgia
 Industry Group: Heavy-duty trucks
 Updated Location: Atlanta, Fulton County
 Address: 605 Stonehill Dr SW, Atlanta, GA 30336
@@ -6272,6 +6454,7 @@
 Source Row ID: 182
 Company: tn americas holding inc.
 Category: OEM Footprint
+State: Georgia
 Industry Group: Commercial vehicles and powertrains
 Updated Location: Cumming, Forsyth County
 Address: 2200 Pendley Rd, Cumming, GA 30041
@@ -6304,6 +6487,7 @@
 Source Row ID: 183
 Company: toyota industries group (tacg-tica)
 Category: OEM Footprint
+State: Georgia
 Industry Group: Commercial vehicles and powertrains
 Updated Location: Pendergrass, Jackson County
 Address: 1000 Valentine Industrial Pkwy, Pendergrass, GA 30567
@@ -6336,6 +6520,7 @@
 Source Row ID: 184
 Company: trenton pressing
 Category: OEM Footprint
+State: Georgia
 Industry Group: Commercial vehicles (Kenworth, Peterbilt)
 Updated Location: Trenton, Dade County
 Address: 505 N Industrial Blvd, Trenton, GA 30752
@@ -6368,6 +6553,7 @@
 Source Row ID: 185
 Company: trenton pressing inc.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive precision components
 Updated Location: Trenton, Dade County
 Address: 505 N Industrial Blvd, Trenton, GA 30752
@@ -6400,6 +6586,7 @@
 Source Row ID: 186
 Company: valeo
 Category: OEM Supply Chain
+State: Unknown
 Industry Group: Automotive parts manufacturing
 Updated Location: Unknown
 Address: Unknown
@@ -6432,6 +6619,7 @@
 Source Row ID: 187
 Company: vanguard national trailer corp.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive structural components
 Updated Location: Trenton, Dade County
 Address: 8 Vanguard Dr, Trenton, GA 30752
@@ -6464,6 +6652,7 @@
 Source Row ID: 188
 Company: vernay
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive stamping and assemblies
 Updated Location: Griffin, Spalding County
 Address: 804 Greenbelt Pkwy, Griffin, GA 30223
@@ -6496,6 +6685,7 @@
 Source Row ID: 189
 Company: vista metals corp.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive modules and components
 Updated Location: Adairsville, Bartow County
 Address: 800 Martin Luther King Jr Dr, Adairsville, GA 30103
@@ -6528,6 +6718,7 @@
 Source Row ID: 190
 Company: voestalpine automotive body parts inc.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive components
 Updated Location: Cartersville, Bartow County
 Address: 4334 Highway 20 SE, Cartersville, GA 30121
@@ -6560,6 +6751,7 @@
 Source Row ID: 191
 Company: volvo cars usa
 Category: OEM Supply Chain
+State: New Jersey
 Industry Group: Automotive plastics
 Updated Location: Rabun County
 Address: 1800 Volvo Place, Mahwah, NJ 07430
@@ -6592,6 +6784,7 @@
 Source Row ID: 192
 Company: volvo group north america
 Category: OEM Supply Chain
+State: North Carolina
 Industry Group: Metal stamping and assemblies
 Updated Location: Lincoln County
 Address: 7900 National Service Rd, Greensboro, NC 27409
@@ -6624,6 +6817,7 @@
 Source Row ID: 193
 Company: wabash national corp.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive plastic components
 Updated Location: Ellenwood, Clayton County
 Address: 2620 Campbell Blvd, Ellenwood, GA 30294
@@ -6656,6 +6850,7 @@
 Source Row ID: 194
 Company: wheelabrator group inc.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive textiles and interiors
 Updated Location: LaGrange, Troup County
 Address: 1606 Executive Dr, LaGrange, GA 30240
@@ -6688,6 +6883,7 @@
 Source Row ID: 195
 Company: wika usa
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive wiring systems
 Updated Location: Lawrenceville, Gwinnett County
 Address: 1000 Wiegand Blvd, Lawrenceville, GA 30043
@@ -6720,6 +6916,7 @@
 Source Row ID: 196
 Company: woodbridge foam corp.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive electrical systems
 Updated Location: Lithonia, DeKalb County
 Address: 2399 S Stone Mountain Lithonia Rd, Lithonia, GA 30058
@@ -6752,6 +6949,7 @@
 Source Row ID: 197
 Company: woory industrial co.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Electrical connectors and sensors
 Updated Location: Dublin, Laurens County
 Address: 404 Kellam Rd, Dublin, GA 31021
@@ -6784,6 +6982,7 @@
 Source Row ID: 198
 Company: yachiyo manufacturing of america llc
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive seating and E‑systems
 Updated Location: Carrollton, Carroll County
 Address: 565 Beulah Church Rd, Carrollton, GA 30117
@@ -6816,6 +7015,7 @@
 Source Row ID: 199
 Company: yamaha motor manufacturing corp.
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive electronics
 Updated Location: Newnan, Coweta County
 Address: 1000 Georgia Highway 34E, Newnan, GA
@@ -6848,6 +7048,7 @@
 Source Row ID: 200
 Company: yazaki north america
 Category: OEM Footprint
+State: Georgia
 Industry Group: Automotive electronics and systems
 Updated Location: Spalding County
 Address: 375 Airport Rd, Griffin, Georgia
@@ -6880,6 +7081,7 @@
 Source Row ID: 201
 Company: ykk usa inc.
 Category: OEM Footprint
+State: Georgia
 Industry Group: Automotive electronics and safety systems
 Updated Location: Marietta, Cobb County
 Address: 1300 Cobb Industrial Dr, Marietta, GA 30066
@@ -6912,6 +7114,7 @@
 Source Row ID: 202
 Company: zf gainesville llc
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive systems and components
 Updated Location: Gainesville, Hall County
 Address: 1261 Palmour Dr SW, Gainesville, GA 30501
@@ -6944,6 +7147,7 @@
 Source Row ID: 203
 Company: zf gainesville llc
 Category: OEM Supply Chain
+State: Georgia
 Industry Group: Automotive thermal and electronics systems
 Updated Location: Gainesville, Hall County
 Address: 1261 Palmour Dr SW, Gainesville, GA 30501
@@ -6976,6 +7180,7 @@
 Source Row ID: 204
 Company: zf gainesville llc
 Category: OEM Footprint
+State: Georgia
 Industry Group: Automotive powertrain and thermal systems
 Updated Location: Gainesville, Hall County
 Address: Unknown
